--- a/docs/templates/modele_initialisation_plateforme_fyp.xlsx
+++ b/docs/templates/modele_initialisation_plateforme_fyp.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCTIONS" sheetId="1" r:id="R8952f5cdec1b4095"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" r:id="Ref66ac5e2e624cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADMINISTRATORS" sheetId="3" r:id="R1331976a4d9044a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COORDINATORS" sheetId="4" r:id="R96fa5012ddae4dd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUPERVISORS" sheetId="5" r:id="Re845a4db0b8147d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACULTY_EVALUATORS" sheetId="6" r:id="R10d889809406443b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDUSTRY_GUESTS" sheetId="7" r:id="R69f6169516594624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJECT_ASSIGNMENTS" sheetId="8" r:id="Rf2c5c5cf9d0c4fb0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCTIONS" sheetId="1" r:id="R9aa971ebc56645d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" r:id="Rf96b9745eb9449d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADMINISTRATORS" sheetId="3" r:id="R4a52b7189df64694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COORDINATORS" sheetId="4" r:id="R6a4d38ce8b5e4e9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUPERVISORS" sheetId="5" r:id="Rb046aec233f441c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACULTY_EVALUATORS" sheetId="6" r:id="R93798dbe796c4e15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDUSTRY_GUESTS" sheetId="7" r:id="R094dc57b810f4802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJECT_ASSIGNMENTS" sheetId="8" r:id="R088c1ecb2cd94f51"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +20,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="4">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="@"/>
+  </x:numFmts>
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -43,8 +46,20 @@
       <x:color rgb="FF102A56"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="18"/>
+      <x:color rgb="FF6B4F00"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B4F00"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -76,8 +91,33 @@
         <x:fgColor rgb="FF7A5A20"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF3CD"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="12">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -158,11 +198,25 @@
         <x:color rgb="FFD5A83E"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD6B656"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD6B656"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD6B656"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD6B656"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="58">
+  <x:cellXfs count="76">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -290,6 +344,54 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="11" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -509,9 +611,11 @@
       <x:c r="G1" s="4"/>
       <x:c r="H1" s="4"/>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="4"/>
-      <x:c r="B2" s="4"/>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="74" t="str">
+        <x:v>FICTIONAL EXAMPLES ONLY - replace or delete every populated example row before a real import.</x:v>
+      </x:c>
+      <x:c r="B2" s="74"/>
       <x:c r="C2" s="4"/>
       <x:c r="D2" s="4"/>
       <x:c r="E2" s="4"/>
@@ -519,6 +623,10 @@
       <x:c r="G2" s="4"/>
       <x:c r="H2" s="4"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="A3"/>
+      <x:c r="B3"/>
+    </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="9" t="str">
         <x:v>Step</x:v>
@@ -532,7 +640,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>Complete STUDENTS with the official university data.</x:v>
+        <x:v>Replace the fictional STUDENTS rows with official university data before import. Students are academic records, not login accounts.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -540,23 +648,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="15" t="str">
-        <x:v>Complete each actor sheet. New actors require a temporary password.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
+        <x:v>Replace internal actor rows with official university identities. Do not provide passwords: actorId and institutional email must match SQU SSO.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="15" t="str">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B7" s="15" t="str">
-        <x:v>Complete PROJECT_ASSIGNMENTS with one student and one supervisor per row.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
+        <x:v>Replace Industry Guest rows, set a future accessExpiresAt, and keep status PENDING_INVITATION. The platform sends each guest a one-time activation link.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="15" t="str">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>Use at most 5 students and 2 supervisors for one project.</x:v>
+        <x:v>In PROJECT_ASSIGNMENTS, repeat projectNumber on continuation rows. Use 1-5 unique students and 1-2 unique supervisors per project.</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -564,7 +672,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>Separate multiple evaluator emails with a semicolon (;).</x:v>
+        <x:v>Separate multiple evaluator emails with a semicolon (;). Industry Guests can only be assigned to Demo Day.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -572,7 +680,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="15" t="str">
-        <x:v>Do not import grades, D3, or the former evaluator workbooks.</x:v>
+        <x:v>Do not import grades, D3, or the former evaluator workbooks. Evaluation forms and final calculations are managed by the platform.</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -580,12 +688,20 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="15" t="str">
-        <x:v>Upload the workbook to Imports Excel and run Preview before Import.</x:v>
+        <x:v>Upload this workbook in Imports Excel and run Preview before Import. One validation error blocks the complete transactional import.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="30" customHeight="1">
+      <x:c r="A12" s="75" t="str">
+        <x:v>IMPORTANT</x:v>
+      </x:c>
+      <x:c r="B12" s="75" t="str">
+        <x:v>All populated rows are fictional examples. Replace or delete them before importing official university data.</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="35" t="str">
-        <x:v>After import, configure FYP I and FYP II dates, deadlines and weights in the platform. The import is transactional: if one validation error exists, no data is saved.</x:v>
+        <x:v>After import: configure FYP I/FYP II dates and deadlines, enable SQU OIDC, and verify Industry invitation emails before Demo Day.</x:v>
       </x:c>
       <x:c r="B13" s="36"/>
       <x:c r="C13" s="36"/>
@@ -657,17 +773,17 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="14" t="str">
-        <x:v>142430</x:v>
+      <x:c r="A2" s="72" t="str">
+        <x:v>99000001</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Ahmed Al Harthy</x:v>
+        <x:v>Example Student 01</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>s142430@student.squ.edu.om</x:v>
+        <x:v>s99000001@student.squ.edu.om</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>2022</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
         <x:v>EIC</x:v>
@@ -677,103 +793,187 @@
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="15" t="str">
-        <x:v>142431</x:v>
+      <x:c r="A3" s="73" t="str">
+        <x:v>99000002</x:v>
       </x:c>
       <x:c r="B3" s="15" t="str">
-        <x:v>Fatma Al Balushi</x:v>
+        <x:v>Example Student 02</x:v>
       </x:c>
       <x:c r="C3" s="15" t="str">
-        <x:v>s142431@student.squ.edu.om</x:v>
+        <x:v>s99000002@student.squ.edu.om</x:v>
       </x:c>
       <x:c r="D3" s="15" t="str">
-        <x:v>2022</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E3" s="15" t="str">
-        <x:v>EIC</x:v>
+        <x:v>CSN</x:v>
       </x:c>
       <x:c r="F3" s="15" t="str">
         <x:v>Final Year</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="15" t="str">
-        <x:v>142432</x:v>
+      <x:c r="A4" s="73" t="str">
+        <x:v>99000003</x:v>
       </x:c>
       <x:c r="B4" s="15" t="str">
-        <x:v>Said Al Habsi</x:v>
+        <x:v>Example Student 03</x:v>
       </x:c>
       <x:c r="C4" s="15" t="str">
-        <x:v>s142432@student.squ.edu.om</x:v>
+        <x:v>s99000003@student.squ.edu.om</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>2022</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="E4" s="15" t="str">
-        <x:v>EIC</x:v>
+        <x:v>CSN</x:v>
       </x:c>
       <x:c r="F4" s="15" t="str">
         <x:v>Final Year</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="15"/>
-      <x:c r="B5" s="15"/>
-      <x:c r="C5" s="15"/>
-      <x:c r="D5" s="15"/>
-      <x:c r="E5" s="15"/>
-      <x:c r="F5" s="15"/>
+      <x:c r="A5" s="73" t="str">
+        <x:v>99000004</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="str">
+        <x:v>Example Student 04</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="str">
+        <x:v>s99000004@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D5" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="str">
+        <x:v>CSP</x:v>
+      </x:c>
+      <x:c r="F5" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="15"/>
-      <x:c r="B6" s="15"/>
-      <x:c r="C6" s="15"/>
-      <x:c r="D6" s="15"/>
-      <x:c r="E6" s="15"/>
-      <x:c r="F6" s="15"/>
+      <x:c r="A6" s="73" t="str">
+        <x:v>99000005</x:v>
+      </x:c>
+      <x:c r="B6" s="15" t="str">
+        <x:v>Example Student 05</x:v>
+      </x:c>
+      <x:c r="C6" s="15" t="str">
+        <x:v>s99000005@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D6" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E6" s="15" t="str">
+        <x:v>CSP</x:v>
+      </x:c>
+      <x:c r="F6" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="15"/>
-      <x:c r="B7" s="15"/>
-      <x:c r="C7" s="15"/>
-      <x:c r="D7" s="15"/>
-      <x:c r="E7" s="15"/>
-      <x:c r="F7" s="15"/>
+      <x:c r="A7" s="73" t="str">
+        <x:v>99000006</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="str">
+        <x:v>Example Student 06</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>s99000006@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="str">
+        <x:v>CSP</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="15"/>
-      <x:c r="B8" s="15"/>
-      <x:c r="C8" s="15"/>
-      <x:c r="D8" s="15"/>
-      <x:c r="E8" s="15"/>
-      <x:c r="F8" s="15"/>
+      <x:c r="A8" s="73" t="str">
+        <x:v>99000007</x:v>
+      </x:c>
+      <x:c r="B8" s="15" t="str">
+        <x:v>Example Student 07</x:v>
+      </x:c>
+      <x:c r="C8" s="15" t="str">
+        <x:v>s99000007@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D8" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E8" s="15" t="str">
+        <x:v>CSP</x:v>
+      </x:c>
+      <x:c r="F8" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="15"/>
-      <x:c r="B9" s="15"/>
-      <x:c r="C9" s="15"/>
-      <x:c r="D9" s="15"/>
-      <x:c r="E9" s="15"/>
-      <x:c r="F9" s="15"/>
+      <x:c r="A9" s="73" t="str">
+        <x:v>99000008</x:v>
+      </x:c>
+      <x:c r="B9" s="15" t="str">
+        <x:v>Example Student 08</x:v>
+      </x:c>
+      <x:c r="C9" s="15" t="str">
+        <x:v>s99000008@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D9" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E9" s="15" t="str">
+        <x:v>CSP</x:v>
+      </x:c>
+      <x:c r="F9" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="15"/>
-      <x:c r="B10" s="15"/>
-      <x:c r="C10" s="15"/>
-      <x:c r="D10" s="15"/>
-      <x:c r="E10" s="15"/>
-      <x:c r="F10" s="15"/>
+      <x:c r="A10" s="73" t="str">
+        <x:v>99000009</x:v>
+      </x:c>
+      <x:c r="B10" s="15" t="str">
+        <x:v>Example Student 09</x:v>
+      </x:c>
+      <x:c r="C10" s="15" t="str">
+        <x:v>s99000009@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D10" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E10" s="15" t="str">
+        <x:v>PSE</x:v>
+      </x:c>
+      <x:c r="F10" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="15"/>
-      <x:c r="B11" s="15"/>
-      <x:c r="C11" s="15"/>
-      <x:c r="D11" s="15"/>
-      <x:c r="E11" s="15"/>
-      <x:c r="F11" s="15"/>
+      <x:c r="A11" s="73" t="str">
+        <x:v>99000010</x:v>
+      </x:c>
+      <x:c r="B11" s="15" t="str">
+        <x:v>Example Student 10</x:v>
+      </x:c>
+      <x:c r="C11" s="15" t="str">
+        <x:v>s99000010@student.squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D11" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="E11" s="15" t="str">
+        <x:v>PSE</x:v>
+      </x:c>
+      <x:c r="F11" s="15" t="str">
+        <x:v>Final Year</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="15"/>
+      <x:c r="A12" s="73"/>
       <x:c r="B12" s="15"/>
       <x:c r="C12" s="15"/>
       <x:c r="D12" s="15"/>
@@ -781,7 +981,7 @@
       <x:c r="F12" s="15"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="15"/>
+      <x:c r="A13" s="73"/>
       <x:c r="B13" s="15"/>
       <x:c r="C13" s="15"/>
       <x:c r="D13" s="15"/>
@@ -789,7 +989,7 @@
       <x:c r="F13" s="15"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="15"/>
+      <x:c r="A14" s="73"/>
       <x:c r="B14" s="15"/>
       <x:c r="C14" s="15"/>
       <x:c r="D14" s="15"/>
@@ -797,7 +997,7 @@
       <x:c r="F14" s="15"/>
     </x:row>
     <x:row r="15">
-      <x:c r="A15" s="15"/>
+      <x:c r="A15" s="73"/>
       <x:c r="B15" s="15"/>
       <x:c r="C15" s="15"/>
       <x:c r="D15" s="15"/>
@@ -805,7 +1005,7 @@
       <x:c r="F15" s="15"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="15"/>
+      <x:c r="A16" s="73"/>
       <x:c r="B16" s="15"/>
       <x:c r="C16" s="15"/>
       <x:c r="D16" s="15"/>
@@ -813,7 +1013,7 @@
       <x:c r="F16" s="15"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="15"/>
+      <x:c r="A17" s="73"/>
       <x:c r="B17" s="15"/>
       <x:c r="C17" s="15"/>
       <x:c r="D17" s="15"/>
@@ -821,7 +1021,7 @@
       <x:c r="F17" s="15"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="15"/>
+      <x:c r="A18" s="73"/>
       <x:c r="B18" s="15"/>
       <x:c r="C18" s="15"/>
       <x:c r="D18" s="15"/>
@@ -829,7 +1029,7 @@
       <x:c r="F18" s="15"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="15"/>
+      <x:c r="A19" s="73"/>
       <x:c r="B19" s="15"/>
       <x:c r="C19" s="15"/>
       <x:c r="D19" s="15"/>
@@ -837,7 +1037,7 @@
       <x:c r="F19" s="15"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="15"/>
+      <x:c r="A20" s="73"/>
       <x:c r="B20" s="15"/>
       <x:c r="C20" s="15"/>
       <x:c r="D20" s="15"/>
@@ -845,7 +1045,7 @@
       <x:c r="F20" s="15"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="15"/>
+      <x:c r="A21" s="73"/>
       <x:c r="B21" s="15"/>
       <x:c r="C21" s="15"/>
       <x:c r="D21" s="15"/>
@@ -853,7 +1053,7 @@
       <x:c r="F21" s="15"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="15"/>
+      <x:c r="A22" s="73"/>
       <x:c r="B22" s="15"/>
       <x:c r="C22" s="15"/>
       <x:c r="D22" s="15"/>
@@ -861,7 +1061,7 @@
       <x:c r="F22" s="15"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="15"/>
+      <x:c r="A23" s="73"/>
       <x:c r="B23" s="15"/>
       <x:c r="C23" s="15"/>
       <x:c r="D23" s="15"/>
@@ -869,7 +1069,7 @@
       <x:c r="F23" s="15"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="15"/>
+      <x:c r="A24" s="73"/>
       <x:c r="B24" s="15"/>
       <x:c r="C24" s="15"/>
       <x:c r="D24" s="15"/>
@@ -877,7 +1077,7 @@
       <x:c r="F24" s="15"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="15"/>
+      <x:c r="A25" s="73"/>
       <x:c r="B25" s="15"/>
       <x:c r="C25" s="15"/>
       <x:c r="D25" s="15"/>
@@ -885,7 +1085,7 @@
       <x:c r="F25" s="15"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="15"/>
+      <x:c r="A26" s="73"/>
       <x:c r="B26" s="15"/>
       <x:c r="C26" s="15"/>
       <x:c r="D26" s="15"/>
@@ -893,7 +1093,7 @@
       <x:c r="F26" s="15"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="15"/>
+      <x:c r="A27" s="73"/>
       <x:c r="B27" s="15"/>
       <x:c r="C27" s="15"/>
       <x:c r="D27" s="15"/>
@@ -901,7 +1101,7 @@
       <x:c r="F27" s="15"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="15"/>
+      <x:c r="A28" s="73"/>
       <x:c r="B28" s="15"/>
       <x:c r="C28" s="15"/>
       <x:c r="D28" s="15"/>
@@ -909,7 +1109,7 @@
       <x:c r="F28" s="15"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="15"/>
+      <x:c r="A29" s="73"/>
       <x:c r="B29" s="15"/>
       <x:c r="C29" s="15"/>
       <x:c r="D29" s="15"/>
@@ -917,7 +1117,7 @@
       <x:c r="F29" s="15"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="15"/>
+      <x:c r="A30" s="73"/>
       <x:c r="B30" s="15"/>
       <x:c r="C30" s="15"/>
       <x:c r="D30" s="15"/>
@@ -925,7 +1125,7 @@
       <x:c r="F30" s="15"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="15"/>
+      <x:c r="A31" s="73"/>
       <x:c r="B31" s="15"/>
       <x:c r="C31" s="15"/>
       <x:c r="D31" s="15"/>
@@ -933,7 +1133,7 @@
       <x:c r="F31" s="15"/>
     </x:row>
     <x:row r="32">
-      <x:c r="A32" s="15"/>
+      <x:c r="A32" s="73"/>
       <x:c r="B32" s="15"/>
       <x:c r="C32" s="15"/>
       <x:c r="D32" s="15"/>
@@ -941,7 +1141,7 @@
       <x:c r="F32" s="15"/>
     </x:row>
     <x:row r="33">
-      <x:c r="A33" s="15"/>
+      <x:c r="A33" s="73"/>
       <x:c r="B33" s="15"/>
       <x:c r="C33" s="15"/>
       <x:c r="D33" s="15"/>
@@ -949,7 +1149,7 @@
       <x:c r="F33" s="15"/>
     </x:row>
     <x:row r="34">
-      <x:c r="A34" s="15"/>
+      <x:c r="A34" s="73"/>
       <x:c r="B34" s="15"/>
       <x:c r="C34" s="15"/>
       <x:c r="D34" s="15"/>
@@ -957,7 +1157,7 @@
       <x:c r="F34" s="15"/>
     </x:row>
     <x:row r="35">
-      <x:c r="A35" s="15"/>
+      <x:c r="A35" s="73"/>
       <x:c r="B35" s="15"/>
       <x:c r="C35" s="15"/>
       <x:c r="D35" s="15"/>
@@ -965,7 +1165,7 @@
       <x:c r="F35" s="15"/>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="15"/>
+      <x:c r="A36" s="73"/>
       <x:c r="B36" s="15"/>
       <x:c r="C36" s="15"/>
       <x:c r="D36" s="15"/>
@@ -973,7 +1173,7 @@
       <x:c r="F36" s="15"/>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="15"/>
+      <x:c r="A37" s="73"/>
       <x:c r="B37" s="15"/>
       <x:c r="C37" s="15"/>
       <x:c r="D37" s="15"/>
@@ -981,7 +1181,7 @@
       <x:c r="F37" s="15"/>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="15"/>
+      <x:c r="A38" s="73"/>
       <x:c r="B38" s="15"/>
       <x:c r="C38" s="15"/>
       <x:c r="D38" s="15"/>
@@ -989,7 +1189,7 @@
       <x:c r="F38" s="15"/>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="15"/>
+      <x:c r="A39" s="73"/>
       <x:c r="B39" s="15"/>
       <x:c r="C39" s="15"/>
       <x:c r="D39" s="15"/>
@@ -997,7 +1197,7 @@
       <x:c r="F39" s="15"/>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="15"/>
+      <x:c r="A40" s="73"/>
       <x:c r="B40" s="15"/>
       <x:c r="C40" s="15"/>
       <x:c r="D40" s="15"/>
@@ -1005,7 +1205,7 @@
       <x:c r="F40" s="15"/>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="15"/>
+      <x:c r="A41" s="73"/>
       <x:c r="B41" s="15"/>
       <x:c r="C41" s="15"/>
       <x:c r="D41" s="15"/>
@@ -1013,7 +1213,7 @@
       <x:c r="F41" s="15"/>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="15"/>
+      <x:c r="A42" s="73"/>
       <x:c r="B42" s="15"/>
       <x:c r="C42" s="15"/>
       <x:c r="D42" s="15"/>
@@ -1021,7 +1221,7 @@
       <x:c r="F42" s="15"/>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="15"/>
+      <x:c r="A43" s="73"/>
       <x:c r="B43" s="15"/>
       <x:c r="C43" s="15"/>
       <x:c r="D43" s="15"/>
@@ -1029,7 +1229,7 @@
       <x:c r="F43" s="15"/>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="15"/>
+      <x:c r="A44" s="73"/>
       <x:c r="B44" s="15"/>
       <x:c r="C44" s="15"/>
       <x:c r="D44" s="15"/>
@@ -1037,7 +1237,7 @@
       <x:c r="F44" s="15"/>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="15"/>
+      <x:c r="A45" s="73"/>
       <x:c r="B45" s="15"/>
       <x:c r="C45" s="15"/>
       <x:c r="D45" s="15"/>
@@ -1045,7 +1245,7 @@
       <x:c r="F45" s="15"/>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="15"/>
+      <x:c r="A46" s="73"/>
       <x:c r="B46" s="15"/>
       <x:c r="C46" s="15"/>
       <x:c r="D46" s="15"/>
@@ -1053,7 +1253,7 @@
       <x:c r="F46" s="15"/>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="15"/>
+      <x:c r="A47" s="73"/>
       <x:c r="B47" s="15"/>
       <x:c r="C47" s="15"/>
       <x:c r="D47" s="15"/>
@@ -1061,7 +1261,7 @@
       <x:c r="F47" s="15"/>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="15"/>
+      <x:c r="A48" s="73"/>
       <x:c r="B48" s="15"/>
       <x:c r="C48" s="15"/>
       <x:c r="D48" s="15"/>
@@ -1069,7 +1269,7 @@
       <x:c r="F48" s="15"/>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="15"/>
+      <x:c r="A49" s="73"/>
       <x:c r="B49" s="15"/>
       <x:c r="C49" s="15"/>
       <x:c r="D49" s="15"/>
@@ -1077,7 +1277,7 @@
       <x:c r="F49" s="15"/>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="15"/>
+      <x:c r="A50" s="73"/>
       <x:c r="B50" s="15"/>
       <x:c r="C50" s="15"/>
       <x:c r="D50" s="15"/>
@@ -1085,7 +1285,7 @@
       <x:c r="F50" s="15"/>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="15"/>
+      <x:c r="A51" s="73"/>
       <x:c r="B51" s="15"/>
       <x:c r="C51" s="15"/>
       <x:c r="D51" s="15"/>
@@ -1093,7 +1293,7 @@
       <x:c r="F51" s="15"/>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="15"/>
+      <x:c r="A52" s="73"/>
       <x:c r="B52" s="15"/>
       <x:c r="C52" s="15"/>
       <x:c r="D52" s="15"/>
@@ -1101,7 +1301,7 @@
       <x:c r="F52" s="15"/>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="15"/>
+      <x:c r="A53" s="73"/>
       <x:c r="B53" s="15"/>
       <x:c r="C53" s="15"/>
       <x:c r="D53" s="15"/>
@@ -1109,7 +1309,7 @@
       <x:c r="F53" s="15"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="15"/>
+      <x:c r="A54" s="73"/>
       <x:c r="B54" s="15"/>
       <x:c r="C54" s="15"/>
       <x:c r="D54" s="15"/>
@@ -1117,7 +1317,7 @@
       <x:c r="F54" s="15"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="15"/>
+      <x:c r="A55" s="73"/>
       <x:c r="B55" s="15"/>
       <x:c r="C55" s="15"/>
       <x:c r="D55" s="15"/>
@@ -1125,7 +1325,7 @@
       <x:c r="F55" s="15"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="15"/>
+      <x:c r="A56" s="73"/>
       <x:c r="B56" s="15"/>
       <x:c r="C56" s="15"/>
       <x:c r="D56" s="15"/>
@@ -1133,7 +1333,7 @@
       <x:c r="F56" s="15"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="15"/>
+      <x:c r="A57" s="73"/>
       <x:c r="B57" s="15"/>
       <x:c r="C57" s="15"/>
       <x:c r="D57" s="15"/>
@@ -1141,7 +1341,7 @@
       <x:c r="F57" s="15"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="15"/>
+      <x:c r="A58" s="73"/>
       <x:c r="B58" s="15"/>
       <x:c r="C58" s="15"/>
       <x:c r="D58" s="15"/>
@@ -1149,7 +1349,7 @@
       <x:c r="F58" s="15"/>
     </x:row>
     <x:row r="59">
-      <x:c r="A59" s="15"/>
+      <x:c r="A59" s="73"/>
       <x:c r="B59" s="15"/>
       <x:c r="C59" s="15"/>
       <x:c r="D59" s="15"/>
@@ -1157,7 +1357,7 @@
       <x:c r="F59" s="15"/>
     </x:row>
     <x:row r="60">
-      <x:c r="A60" s="15"/>
+      <x:c r="A60" s="73"/>
       <x:c r="B60" s="15"/>
       <x:c r="C60" s="15"/>
       <x:c r="D60" s="15"/>
@@ -1165,7 +1365,7 @@
       <x:c r="F60" s="15"/>
     </x:row>
     <x:row r="61">
-      <x:c r="A61" s="15"/>
+      <x:c r="A61" s="73"/>
       <x:c r="B61" s="15"/>
       <x:c r="C61" s="15"/>
       <x:c r="D61" s="15"/>
@@ -1173,7 +1373,7 @@
       <x:c r="F61" s="15"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="15"/>
+      <x:c r="A62" s="73"/>
       <x:c r="B62" s="15"/>
       <x:c r="C62" s="15"/>
       <x:c r="D62" s="15"/>
@@ -1181,7 +1381,7 @@
       <x:c r="F62" s="15"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="15"/>
+      <x:c r="A63" s="73"/>
       <x:c r="B63" s="15"/>
       <x:c r="C63" s="15"/>
       <x:c r="D63" s="15"/>
@@ -1189,7 +1389,7 @@
       <x:c r="F63" s="15"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="15"/>
+      <x:c r="A64" s="73"/>
       <x:c r="B64" s="15"/>
       <x:c r="C64" s="15"/>
       <x:c r="D64" s="15"/>
@@ -1197,7 +1397,7 @@
       <x:c r="F64" s="15"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="15"/>
+      <x:c r="A65" s="73"/>
       <x:c r="B65" s="15"/>
       <x:c r="C65" s="15"/>
       <x:c r="D65" s="15"/>
@@ -1205,7 +1405,7 @@
       <x:c r="F65" s="15"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="15"/>
+      <x:c r="A66" s="73"/>
       <x:c r="B66" s="15"/>
       <x:c r="C66" s="15"/>
       <x:c r="D66" s="15"/>
@@ -1213,7 +1413,7 @@
       <x:c r="F66" s="15"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="15"/>
+      <x:c r="A67" s="73"/>
       <x:c r="B67" s="15"/>
       <x:c r="C67" s="15"/>
       <x:c r="D67" s="15"/>
@@ -1221,7 +1421,7 @@
       <x:c r="F67" s="15"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="15"/>
+      <x:c r="A68" s="73"/>
       <x:c r="B68" s="15"/>
       <x:c r="C68" s="15"/>
       <x:c r="D68" s="15"/>
@@ -1229,7 +1429,7 @@
       <x:c r="F68" s="15"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="15"/>
+      <x:c r="A69" s="73"/>
       <x:c r="B69" s="15"/>
       <x:c r="C69" s="15"/>
       <x:c r="D69" s="15"/>
@@ -1237,7 +1437,7 @@
       <x:c r="F69" s="15"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="15"/>
+      <x:c r="A70" s="73"/>
       <x:c r="B70" s="15"/>
       <x:c r="C70" s="15"/>
       <x:c r="D70" s="15"/>
@@ -1245,7 +1445,7 @@
       <x:c r="F70" s="15"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="15"/>
+      <x:c r="A71" s="73"/>
       <x:c r="B71" s="15"/>
       <x:c r="C71" s="15"/>
       <x:c r="D71" s="15"/>
@@ -1253,7 +1453,7 @@
       <x:c r="F71" s="15"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="15"/>
+      <x:c r="A72" s="73"/>
       <x:c r="B72" s="15"/>
       <x:c r="C72" s="15"/>
       <x:c r="D72" s="15"/>
@@ -1261,7 +1461,7 @@
       <x:c r="F72" s="15"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="15"/>
+      <x:c r="A73" s="73"/>
       <x:c r="B73" s="15"/>
       <x:c r="C73" s="15"/>
       <x:c r="D73" s="15"/>
@@ -1269,7 +1469,7 @@
       <x:c r="F73" s="15"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="15"/>
+      <x:c r="A74" s="73"/>
       <x:c r="B74" s="15"/>
       <x:c r="C74" s="15"/>
       <x:c r="D74" s="15"/>
@@ -1277,7 +1477,7 @@
       <x:c r="F74" s="15"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="15"/>
+      <x:c r="A75" s="73"/>
       <x:c r="B75" s="15"/>
       <x:c r="C75" s="15"/>
       <x:c r="D75" s="15"/>
@@ -1285,7 +1485,7 @@
       <x:c r="F75" s="15"/>
     </x:row>
     <x:row r="76">
-      <x:c r="A76" s="15"/>
+      <x:c r="A76" s="73"/>
       <x:c r="B76" s="15"/>
       <x:c r="C76" s="15"/>
       <x:c r="D76" s="15"/>
@@ -1293,7 +1493,7 @@
       <x:c r="F76" s="15"/>
     </x:row>
     <x:row r="77">
-      <x:c r="A77" s="15"/>
+      <x:c r="A77" s="73"/>
       <x:c r="B77" s="15"/>
       <x:c r="C77" s="15"/>
       <x:c r="D77" s="15"/>
@@ -1301,7 +1501,7 @@
       <x:c r="F77" s="15"/>
     </x:row>
     <x:row r="78">
-      <x:c r="A78" s="15"/>
+      <x:c r="A78" s="73"/>
       <x:c r="B78" s="15"/>
       <x:c r="C78" s="15"/>
       <x:c r="D78" s="15"/>
@@ -1309,7 +1509,7 @@
       <x:c r="F78" s="15"/>
     </x:row>
     <x:row r="79">
-      <x:c r="A79" s="15"/>
+      <x:c r="A79" s="73"/>
       <x:c r="B79" s="15"/>
       <x:c r="C79" s="15"/>
       <x:c r="D79" s="15"/>
@@ -1317,7 +1517,7 @@
       <x:c r="F79" s="15"/>
     </x:row>
     <x:row r="80">
-      <x:c r="A80" s="15"/>
+      <x:c r="A80" s="73"/>
       <x:c r="B80" s="15"/>
       <x:c r="C80" s="15"/>
       <x:c r="D80" s="15"/>
@@ -1325,7 +1525,7 @@
       <x:c r="F80" s="15"/>
     </x:row>
     <x:row r="81">
-      <x:c r="A81" s="15"/>
+      <x:c r="A81" s="73"/>
       <x:c r="B81" s="15"/>
       <x:c r="C81" s="15"/>
       <x:c r="D81" s="15"/>
@@ -1333,7 +1533,7 @@
       <x:c r="F81" s="15"/>
     </x:row>
     <x:row r="82">
-      <x:c r="A82" s="15"/>
+      <x:c r="A82" s="73"/>
       <x:c r="B82" s="15"/>
       <x:c r="C82" s="15"/>
       <x:c r="D82" s="15"/>
@@ -1341,7 +1541,7 @@
       <x:c r="F82" s="15"/>
     </x:row>
     <x:row r="83">
-      <x:c r="A83" s="15"/>
+      <x:c r="A83" s="73"/>
       <x:c r="B83" s="15"/>
       <x:c r="C83" s="15"/>
       <x:c r="D83" s="15"/>
@@ -1349,7 +1549,7 @@
       <x:c r="F83" s="15"/>
     </x:row>
     <x:row r="84">
-      <x:c r="A84" s="15"/>
+      <x:c r="A84" s="73"/>
       <x:c r="B84" s="15"/>
       <x:c r="C84" s="15"/>
       <x:c r="D84" s="15"/>
@@ -1357,7 +1557,7 @@
       <x:c r="F84" s="15"/>
     </x:row>
     <x:row r="85">
-      <x:c r="A85" s="15"/>
+      <x:c r="A85" s="73"/>
       <x:c r="B85" s="15"/>
       <x:c r="C85" s="15"/>
       <x:c r="D85" s="15"/>
@@ -1365,7 +1565,7 @@
       <x:c r="F85" s="15"/>
     </x:row>
     <x:row r="86">
-      <x:c r="A86" s="15"/>
+      <x:c r="A86" s="73"/>
       <x:c r="B86" s="15"/>
       <x:c r="C86" s="15"/>
       <x:c r="D86" s="15"/>
@@ -1373,7 +1573,7 @@
       <x:c r="F86" s="15"/>
     </x:row>
     <x:row r="87">
-      <x:c r="A87" s="15"/>
+      <x:c r="A87" s="73"/>
       <x:c r="B87" s="15"/>
       <x:c r="C87" s="15"/>
       <x:c r="D87" s="15"/>
@@ -1381,7 +1581,7 @@
       <x:c r="F87" s="15"/>
     </x:row>
     <x:row r="88">
-      <x:c r="A88" s="15"/>
+      <x:c r="A88" s="73"/>
       <x:c r="B88" s="15"/>
       <x:c r="C88" s="15"/>
       <x:c r="D88" s="15"/>
@@ -1389,7 +1589,7 @@
       <x:c r="F88" s="15"/>
     </x:row>
     <x:row r="89">
-      <x:c r="A89" s="15"/>
+      <x:c r="A89" s="73"/>
       <x:c r="B89" s="15"/>
       <x:c r="C89" s="15"/>
       <x:c r="D89" s="15"/>
@@ -1397,7 +1597,7 @@
       <x:c r="F89" s="15"/>
     </x:row>
     <x:row r="90">
-      <x:c r="A90" s="15"/>
+      <x:c r="A90" s="73"/>
       <x:c r="B90" s="15"/>
       <x:c r="C90" s="15"/>
       <x:c r="D90" s="15"/>
@@ -1405,7 +1605,7 @@
       <x:c r="F90" s="15"/>
     </x:row>
     <x:row r="91">
-      <x:c r="A91" s="15"/>
+      <x:c r="A91" s="73"/>
       <x:c r="B91" s="15"/>
       <x:c r="C91" s="15"/>
       <x:c r="D91" s="15"/>
@@ -1413,7 +1613,7 @@
       <x:c r="F91" s="15"/>
     </x:row>
     <x:row r="92">
-      <x:c r="A92" s="15"/>
+      <x:c r="A92" s="73"/>
       <x:c r="B92" s="15"/>
       <x:c r="C92" s="15"/>
       <x:c r="D92" s="15"/>
@@ -1421,7 +1621,7 @@
       <x:c r="F92" s="15"/>
     </x:row>
     <x:row r="93">
-      <x:c r="A93" s="15"/>
+      <x:c r="A93" s="73"/>
       <x:c r="B93" s="15"/>
       <x:c r="C93" s="15"/>
       <x:c r="D93" s="15"/>
@@ -1429,7 +1629,7 @@
       <x:c r="F93" s="15"/>
     </x:row>
     <x:row r="94">
-      <x:c r="A94" s="15"/>
+      <x:c r="A94" s="73"/>
       <x:c r="B94" s="15"/>
       <x:c r="C94" s="15"/>
       <x:c r="D94" s="15"/>
@@ -1437,7 +1637,7 @@
       <x:c r="F94" s="15"/>
     </x:row>
     <x:row r="95">
-      <x:c r="A95" s="15"/>
+      <x:c r="A95" s="73"/>
       <x:c r="B95" s="15"/>
       <x:c r="C95" s="15"/>
       <x:c r="D95" s="15"/>
@@ -1445,7 +1645,7 @@
       <x:c r="F95" s="15"/>
     </x:row>
     <x:row r="96">
-      <x:c r="A96" s="15"/>
+      <x:c r="A96" s="73"/>
       <x:c r="B96" s="15"/>
       <x:c r="C96" s="15"/>
       <x:c r="D96" s="15"/>
@@ -1453,7 +1653,7 @@
       <x:c r="F96" s="15"/>
     </x:row>
     <x:row r="97">
-      <x:c r="A97" s="15"/>
+      <x:c r="A97" s="73"/>
       <x:c r="B97" s="15"/>
       <x:c r="C97" s="15"/>
       <x:c r="D97" s="15"/>
@@ -1461,7 +1661,7 @@
       <x:c r="F97" s="15"/>
     </x:row>
     <x:row r="98">
-      <x:c r="A98" s="15"/>
+      <x:c r="A98" s="73"/>
       <x:c r="B98" s="15"/>
       <x:c r="C98" s="15"/>
       <x:c r="D98" s="15"/>
@@ -1469,7 +1669,7 @@
       <x:c r="F98" s="15"/>
     </x:row>
     <x:row r="99">
-      <x:c r="A99" s="15"/>
+      <x:c r="A99" s="73"/>
       <x:c r="B99" s="15"/>
       <x:c r="C99" s="15"/>
       <x:c r="D99" s="15"/>
@@ -1477,7 +1677,7 @@
       <x:c r="F99" s="15"/>
     </x:row>
     <x:row r="100">
-      <x:c r="A100" s="15"/>
+      <x:c r="A100" s="73"/>
       <x:c r="B100" s="15"/>
       <x:c r="C100" s="15"/>
       <x:c r="D100" s="15"/>
@@ -2335,7 +2535,7 @@
         <x:v>phone</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>authenticationMode</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
         <x:v>status</x:v>
@@ -2343,28 +2543,28 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>ADMIN-02</x:v>
+        <x:v>DEMO-ADMIN-01</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>FYP Administrator</x:v>
+        <x:v>Example Administrator</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>fyp.admin@squ.edu.om</x:v>
+        <x:v>demo.admin@squ.edu.om</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Electrical Engineering</x:v>
+        <x:v>Example Engineering Department</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>FYP Administration</x:v>
+        <x:v>Example FYP Administration</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>SQU</x:v>
+        <x:v>Example University Unit</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>+96890000001</x:v>
+        <x:v>EXAMPLE-PHONE-01</x:v>
       </x:c>
       <x:c r="H2" s="14" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>SQU_SSO</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
         <x:v>ACTIVE</x:v>
@@ -2616,7 +2816,7 @@
         <x:v>phone</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>authenticationMode</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
         <x:v>status</x:v>
@@ -2624,28 +2824,28 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>COORD-01</x:v>
+        <x:v>DEMO-COORD-01</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Dr FYP Coordinator</x:v>
+        <x:v>Example Coordinator</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>fyp.coordinator@squ.edu.om</x:v>
+        <x:v>demo.coordinator@squ.edu.om</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Electrical Engineering</x:v>
+        <x:v>Example Engineering Department</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>FYP Coordination</x:v>
+        <x:v>Example FYP Coordination</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>SQU</x:v>
+        <x:v>Example University Unit</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>+96890000002</x:v>
+        <x:v>EXAMPLE-PHONE-02</x:v>
       </x:c>
       <x:c r="H2" s="14" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>SQU_SSO</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
         <x:v>ACTIVE</x:v>
@@ -2897,7 +3097,7 @@
         <x:v>phone</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>authenticationMode</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
         <x:v>status</x:v>
@@ -2905,28 +3105,28 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>SUP-EIC-01</x:v>
+        <x:v>DEMO-SUP-01</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Dr Sara Al Maawali</x:v>
+        <x:v>Example Supervisor Alpha</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>sara.supervisor@squ.edu.om</x:v>
+        <x:v>demo.supervisor01@squ.edu.om</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Electrical Engineering</x:v>
+        <x:v>Example Engineering Department</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>Embedded Systems</x:v>
+        <x:v>Example Embedded Systems</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>SQU</x:v>
+        <x:v>Example University Unit</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>+96890000003</x:v>
+        <x:v>EXAMPLE-PHONE-03</x:v>
       </x:c>
       <x:c r="H2" s="14" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>SQU_SSO</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
         <x:v>ACTIVE</x:v>
@@ -2934,54 +3134,90 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="15" t="str">
-        <x:v>SUP-EIC-02</x:v>
+        <x:v>DEMO-SUP-02</x:v>
       </x:c>
       <x:c r="B3" s="15" t="str">
-        <x:v>Dr Khalid Al Shanfari</x:v>
+        <x:v>Example Supervisor Beta</x:v>
       </x:c>
       <x:c r="C3" s="15" t="str">
-        <x:v>khalid.supervisor@squ.edu.om</x:v>
+        <x:v>demo.supervisor02@squ.edu.om</x:v>
       </x:c>
       <x:c r="D3" s="15" t="str">
-        <x:v>Electrical Engineering</x:v>
+        <x:v>Example Engineering Department</x:v>
       </x:c>
       <x:c r="E3" s="15" t="str">
-        <x:v>Control Systems</x:v>
+        <x:v>Example Control Systems</x:v>
       </x:c>
       <x:c r="F3" s="15" t="str">
-        <x:v>SQU</x:v>
+        <x:v>Example University Unit</x:v>
       </x:c>
       <x:c r="G3" s="15" t="str">
-        <x:v>+96890000004</x:v>
+        <x:v>EXAMPLE-PHONE-04</x:v>
       </x:c>
       <x:c r="H3" s="15" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>SQU_SSO</x:v>
       </x:c>
       <x:c r="I3" s="15" t="str">
         <x:v>ACTIVE</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="15"/>
-      <x:c r="B4" s="15"/>
-      <x:c r="C4" s="15"/>
-      <x:c r="D4" s="15"/>
-      <x:c r="E4" s="15"/>
-      <x:c r="F4" s="15"/>
-      <x:c r="G4" s="15"/>
-      <x:c r="H4" s="15"/>
-      <x:c r="I4" s="15"/>
+      <x:c r="A4" s="15" t="str">
+        <x:v>DEMO-SUP-03</x:v>
+      </x:c>
+      <x:c r="B4" s="15" t="str">
+        <x:v>Example Supervisor Gamma</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="str">
+        <x:v>demo.supervisor03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D4" s="15" t="str">
+        <x:v>Example Engineering Department</x:v>
+      </x:c>
+      <x:c r="E4" s="15" t="str">
+        <x:v>Example Networks</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="str">
+        <x:v>Example University Unit</x:v>
+      </x:c>
+      <x:c r="G4" s="15" t="str">
+        <x:v>EXAMPLE-PHONE-05</x:v>
+      </x:c>
+      <x:c r="H4" s="15" t="str">
+        <x:v>SQU_SSO</x:v>
+      </x:c>
+      <x:c r="I4" s="15" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="15"/>
-      <x:c r="B5" s="15"/>
-      <x:c r="C5" s="15"/>
-      <x:c r="D5" s="15"/>
-      <x:c r="E5" s="15"/>
-      <x:c r="F5" s="15"/>
-      <x:c r="G5" s="15"/>
-      <x:c r="H5" s="15"/>
-      <x:c r="I5" s="15"/>
+      <x:c r="A5" s="15" t="str">
+        <x:v>DEMO-SUP-04</x:v>
+      </x:c>
+      <x:c r="B5" s="15" t="str">
+        <x:v>Example Supervisor Delta</x:v>
+      </x:c>
+      <x:c r="C5" s="15" t="str">
+        <x:v>demo.supervisor04@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D5" s="15" t="str">
+        <x:v>Example Engineering Department</x:v>
+      </x:c>
+      <x:c r="E5" s="15" t="str">
+        <x:v>Example Power Systems</x:v>
+      </x:c>
+      <x:c r="F5" s="15" t="str">
+        <x:v>Example University Unit</x:v>
+      </x:c>
+      <x:c r="G5" s="15" t="str">
+        <x:v>EXAMPLE-PHONE-06</x:v>
+      </x:c>
+      <x:c r="H5" s="15" t="str">
+        <x:v>SQU_SSO</x:v>
+      </x:c>
+      <x:c r="I5" s="15" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="15"/>
@@ -3196,7 +3432,7 @@
         <x:v>phone</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>authenticationMode</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
         <x:v>status</x:v>
@@ -3204,28 +3440,28 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>FAC-01</x:v>
+        <x:v>DEMO-FAC-01</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Dr Reem Al Hinai</x:v>
+        <x:v>Example Faculty Evaluator Alpha</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>reem.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty01@squ.edu.om</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Electrical Engineering</x:v>
+        <x:v>Example Engineering Department</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>Power Systems</x:v>
+        <x:v>Example Power Systems</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>SQU</x:v>
+        <x:v>Example University Unit</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>+96890000005</x:v>
+        <x:v>EXAMPLE-PHONE-07</x:v>
       </x:c>
       <x:c r="H2" s="14" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>SQU_SSO</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
         <x:v>ACTIVE</x:v>
@@ -3233,43 +3469,61 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="15" t="str">
-        <x:v>FAC-02</x:v>
+        <x:v>DEMO-FAC-02</x:v>
       </x:c>
       <x:c r="B3" s="15" t="str">
-        <x:v>Dr Said Al Rawahi</x:v>
+        <x:v>Example Faculty Evaluator Beta</x:v>
       </x:c>
       <x:c r="C3" s="15" t="str">
-        <x:v>said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty02@squ.edu.om</x:v>
       </x:c>
       <x:c r="D3" s="15" t="str">
-        <x:v>Electrical Engineering</x:v>
+        <x:v>Example Engineering Department</x:v>
       </x:c>
       <x:c r="E3" s="15" t="str">
-        <x:v>Networks</x:v>
+        <x:v>Example Networks</x:v>
       </x:c>
       <x:c r="F3" s="15" t="str">
-        <x:v>SQU</x:v>
+        <x:v>Example University Unit</x:v>
       </x:c>
       <x:c r="G3" s="15" t="str">
-        <x:v>+96890000006</x:v>
+        <x:v>EXAMPLE-PHONE-08</x:v>
       </x:c>
       <x:c r="H3" s="15" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>SQU_SSO</x:v>
       </x:c>
       <x:c r="I3" s="15" t="str">
         <x:v>ACTIVE</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="15"/>
-      <x:c r="B4" s="15"/>
-      <x:c r="C4" s="15"/>
-      <x:c r="D4" s="15"/>
-      <x:c r="E4" s="15"/>
-      <x:c r="F4" s="15"/>
-      <x:c r="G4" s="15"/>
-      <x:c r="H4" s="15"/>
-      <x:c r="I4" s="15"/>
+      <x:c r="A4" s="15" t="str">
+        <x:v>DEMO-FAC-03</x:v>
+      </x:c>
+      <x:c r="B4" s="15" t="str">
+        <x:v>Example Faculty Evaluator Gamma</x:v>
+      </x:c>
+      <x:c r="C4" s="15" t="str">
+        <x:v>demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="D4" s="15" t="str">
+        <x:v>Example Engineering Department</x:v>
+      </x:c>
+      <x:c r="E4" s="15" t="str">
+        <x:v>Example Software Systems</x:v>
+      </x:c>
+      <x:c r="F4" s="15" t="str">
+        <x:v>Example University Unit</x:v>
+      </x:c>
+      <x:c r="G4" s="15" t="str">
+        <x:v>EXAMPLE-PHONE-09</x:v>
+      </x:c>
+      <x:c r="H4" s="15" t="str">
+        <x:v>SQU_SSO</x:v>
+      </x:c>
+      <x:c r="I4" s="15" t="str">
+        <x:v>ACTIVE</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="15"/>
@@ -3468,8 +3722,8 @@
     <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="24" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="34" customHeight="1">
@@ -3495,7 +3749,7 @@
         <x:v>phone</x:v>
       </x:c>
       <x:c r="H1" s="9" t="str">
-        <x:v>temporaryPassword</x:v>
+        <x:v>accessExpiresAt</x:v>
       </x:c>
       <x:c r="I1" s="9" t="str">
         <x:v>status</x:v>
@@ -3503,43 +3757,61 @@
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="14" t="str">
-        <x:v>IND-01</x:v>
+        <x:v>DEMO-IND-01</x:v>
       </x:c>
       <x:c r="B2" s="14" t="str">
-        <x:v>Laila Al Lawati</x:v>
+        <x:v>Example Industry Guest Alpha</x:v>
       </x:c>
       <x:c r="C2" s="14" t="str">
-        <x:v>laila.industry@example.com</x:v>
+        <x:v>demo.industry01@example.com</x:v>
       </x:c>
       <x:c r="D2" s="14" t="str">
-        <x:v>Engineering</x:v>
+        <x:v>Example Engineering</x:v>
       </x:c>
       <x:c r="E2" s="14" t="str">
-        <x:v>Industrial Innovation</x:v>
+        <x:v>Example Industrial Innovation</x:v>
       </x:c>
       <x:c r="F2" s="14" t="str">
-        <x:v>Oman Technology Company</x:v>
+        <x:v>Example Technology Company</x:v>
       </x:c>
       <x:c r="G2" s="14" t="str">
-        <x:v>+96890000007</x:v>
+        <x:v>EXAMPLE-PHONE-10</x:v>
       </x:c>
       <x:c r="H2" s="14" t="str">
-        <x:v>Welcome@2026</x:v>
+        <x:v>2027-06-30T23:59</x:v>
       </x:c>
       <x:c r="I2" s="14" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_INVITATION</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="15"/>
-      <x:c r="B3" s="15"/>
-      <x:c r="C3" s="15"/>
-      <x:c r="D3" s="15"/>
-      <x:c r="E3" s="15"/>
-      <x:c r="F3" s="15"/>
-      <x:c r="G3" s="15"/>
-      <x:c r="H3" s="15"/>
-      <x:c r="I3" s="15"/>
+      <x:c r="A3" s="15" t="str">
+        <x:v>DEMO-IND-02</x:v>
+      </x:c>
+      <x:c r="B3" s="15" t="str">
+        <x:v>Example Industry Guest Beta</x:v>
+      </x:c>
+      <x:c r="C3" s="15" t="str">
+        <x:v>demo.industry02@example.com</x:v>
+      </x:c>
+      <x:c r="D3" s="15" t="str">
+        <x:v>Example Engineering</x:v>
+      </x:c>
+      <x:c r="E3" s="15" t="str">
+        <x:v>Example Energy Innovation</x:v>
+      </x:c>
+      <x:c r="F3" s="15" t="str">
+        <x:v>Example Energy Company</x:v>
+      </x:c>
+      <x:c r="G3" s="15" t="str">
+        <x:v>EXAMPLE-PHONE-11</x:v>
+      </x:c>
+      <x:c r="H3" s="15" t="str">
+        <x:v>2027-06-30T23:59</x:v>
+      </x:c>
+      <x:c r="I3" s="15" t="str">
+        <x:v>PENDING_INVITATION</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="15"/>
@@ -3769,11 +4041,11 @@
       <x:c r="E1" s="45"/>
       <x:c r="F1" s="45"/>
       <x:c r="G1" s="49" t="str">
-        <x:v>STUDENT</x:v>
+        <x:v>STUDENT (OPTIONAL)</x:v>
       </x:c>
       <x:c r="H1" s="49"/>
       <x:c r="I1" s="53" t="str">
-        <x:v>SUPERVISOR</x:v>
+        <x:v>SUPERVISOR (MAX 2)</x:v>
       </x:c>
       <x:c r="J1" s="53"/>
       <x:c r="K1" s="57" t="str">
@@ -3831,152 +4103,138 @@
         <x:v>industryGuestEmails</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="14" t="str">
-        <x:v>2022</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="B3" s="14" t="str">
         <x:v>EIC</x:v>
       </x:c>
       <x:c r="C3" s="14" t="str">
-        <x:v>EIC-01</x:v>
+        <x:v>DEMO-EIC-01</x:v>
       </x:c>
       <x:c r="D3" s="14" t="str">
-        <x:v>Smart Laboratory Energy Controller</x:v>
+        <x:v>Example Single-Student Control Project</x:v>
       </x:c>
       <x:c r="E3" s="14" t="str">
-        <x:v>Embedded monitoring and control for laboratory energy consumption.</x:v>
+        <x:v>Fictional example demonstrating one student with two supervisors.</x:v>
       </x:c>
       <x:c r="F3" s="14" t="str">
-        <x:v>EIC-A</x:v>
-      </x:c>
-      <x:c r="G3" s="14" t="str">
-        <x:v>142430</x:v>
+        <x:v>EIC-DEMO</x:v>
+      </x:c>
+      <x:c r="G3" s="72" t="str">
+        <x:v>99000001</x:v>
       </x:c>
       <x:c r="H3" s="14" t="str">
-        <x:v>Ahmed Al Harthy</x:v>
+        <x:v>Example Student 01</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
-        <x:v>SUP-EIC-01</x:v>
+        <x:v>DEMO-SUP-01</x:v>
       </x:c>
       <x:c r="J3" s="14" t="str">
-        <x:v>Dr Sara Al Maawali</x:v>
+        <x:v>Example Supervisor Alpha</x:v>
       </x:c>
       <x:c r="K3" s="14" t="str">
-        <x:v>reem.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty01@squ.edu.om</x:v>
       </x:c>
       <x:c r="L3" s="14" t="str">
-        <x:v>reem.faculty@squ.edu.om;said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty01@squ.edu.om;demo.faculty02@squ.edu.om</x:v>
       </x:c>
       <x:c r="M3" s="14" t="str">
-        <x:v>said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty02@squ.edu.om</x:v>
       </x:c>
       <x:c r="N3" s="14" t="str">
-        <x:v>reem.faculty@squ.edu.om;said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty02@squ.edu.om;demo.faculty03@squ.edu.om</x:v>
       </x:c>
       <x:c r="O3" s="14" t="str">
-        <x:v>laila.industry@example.com</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="15" t="str">
-        <x:v>2022</x:v>
-      </x:c>
-      <x:c r="B4" s="15" t="str">
-        <x:v>EIC</x:v>
-      </x:c>
+        <x:v>demo.industry01@example.com</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="34" customHeight="1">
+      <x:c r="A4" s="15"/>
+      <x:c r="B4" s="15"/>
       <x:c r="C4" s="15" t="str">
-        <x:v>EIC-01</x:v>
-      </x:c>
-      <x:c r="D4" s="15" t="str">
-        <x:v>Smart Laboratory Energy Controller</x:v>
-      </x:c>
-      <x:c r="E4" s="15" t="str">
-        <x:v>Embedded monitoring and control for laboratory energy consumption.</x:v>
-      </x:c>
-      <x:c r="F4" s="15" t="str">
-        <x:v>EIC-A</x:v>
-      </x:c>
-      <x:c r="G4" s="15" t="str">
-        <x:v>142431</x:v>
-      </x:c>
-      <x:c r="H4" s="15" t="str">
-        <x:v>Fatma Al Balushi</x:v>
-      </x:c>
+        <x:v>DEMO-EIC-01</x:v>
+      </x:c>
+      <x:c r="D4" s="15"/>
+      <x:c r="E4" s="15"/>
+      <x:c r="F4" s="15"/>
+      <x:c r="G4" s="73"/>
+      <x:c r="H4" s="15"/>
       <x:c r="I4" s="15" t="str">
-        <x:v>SUP-EIC-02</x:v>
+        <x:v>DEMO-SUP-02</x:v>
       </x:c>
       <x:c r="J4" s="15" t="str">
-        <x:v>Dr Khalid Al Shanfari</x:v>
-      </x:c>
-      <x:c r="K4" s="15" t="str">
-        <x:v>reem.faculty@squ.edu.om</x:v>
-      </x:c>
-      <x:c r="L4" s="15" t="str">
-        <x:v>reem.faculty@squ.edu.om;said.faculty@squ.edu.om</x:v>
-      </x:c>
-      <x:c r="M4" s="15" t="str">
-        <x:v>said.faculty@squ.edu.om</x:v>
-      </x:c>
-      <x:c r="N4" s="15" t="str">
-        <x:v>reem.faculty@squ.edu.om;said.faculty@squ.edu.om</x:v>
-      </x:c>
-      <x:c r="O4" s="15" t="str">
-        <x:v>laila.industry@example.com</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>Example Supervisor Beta</x:v>
+      </x:c>
+      <x:c r="K4" s="15"/>
+      <x:c r="L4" s="15"/>
+      <x:c r="M4" s="15"/>
+      <x:c r="N4" s="15"/>
+      <x:c r="O4" s="15"/>
+    </x:row>
+    <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="15" t="str">
-        <x:v>2022</x:v>
+        <x:v>2027</x:v>
       </x:c>
       <x:c r="B5" s="15" t="str">
-        <x:v>EIC</x:v>
+        <x:v>CSN</x:v>
       </x:c>
       <x:c r="C5" s="15" t="str">
-        <x:v>EIC-01</x:v>
+        <x:v>DEMO-CSN-02</x:v>
       </x:c>
       <x:c r="D5" s="15" t="str">
-        <x:v>Smart Laboratory Energy Controller</x:v>
+        <x:v>Example Network Monitoring Project</x:v>
       </x:c>
       <x:c r="E5" s="15" t="str">
-        <x:v>Embedded monitoring and control for laboratory energy consumption.</x:v>
+        <x:v>Fictional example demonstrating two students with one supervisor.</x:v>
       </x:c>
       <x:c r="F5" s="15" t="str">
-        <x:v>EIC-A</x:v>
-      </x:c>
-      <x:c r="G5" s="15" t="str">
-        <x:v>142432</x:v>
+        <x:v>CSN-DEMO</x:v>
+      </x:c>
+      <x:c r="G5" s="73" t="str">
+        <x:v>99000002</x:v>
       </x:c>
       <x:c r="H5" s="15" t="str">
-        <x:v>Said Al Habsi</x:v>
-      </x:c>
-      <x:c r="I5" s="15" t="str"/>
-      <x:c r="J5" s="15" t="str"/>
+        <x:v>Example Student 02</x:v>
+      </x:c>
+      <x:c r="I5" s="15" t="str">
+        <x:v>DEMO-SUP-03</x:v>
+      </x:c>
+      <x:c r="J5" s="15" t="str">
+        <x:v>Example Supervisor Gamma</x:v>
+      </x:c>
       <x:c r="K5" s="15" t="str">
-        <x:v>reem.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty02@squ.edu.om</x:v>
       </x:c>
       <x:c r="L5" s="15" t="str">
-        <x:v>reem.faculty@squ.edu.om;said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty02@squ.edu.om</x:v>
       </x:c>
       <x:c r="M5" s="15" t="str">
-        <x:v>said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty03@squ.edu.om</x:v>
       </x:c>
       <x:c r="N5" s="15" t="str">
-        <x:v>reem.faculty@squ.edu.om;said.faculty@squ.edu.om</x:v>
+        <x:v>demo.faculty03@squ.edu.om</x:v>
       </x:c>
       <x:c r="O5" s="15" t="str">
-        <x:v>laila.industry@example.com</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
+        <x:v>demo.industry01@example.com</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="15"/>
       <x:c r="B6" s="15"/>
-      <x:c r="C6" s="15"/>
+      <x:c r="C6" s="15" t="str">
+        <x:v>DEMO-CSN-02</x:v>
+      </x:c>
       <x:c r="D6" s="15"/>
       <x:c r="E6" s="15"/>
       <x:c r="F6" s="15"/>
-      <x:c r="G6" s="15"/>
-      <x:c r="H6" s="15"/>
+      <x:c r="G6" s="73" t="str">
+        <x:v>99000003</x:v>
+      </x:c>
+      <x:c r="H6" s="15" t="str">
+        <x:v>Example Student 03</x:v>
+      </x:c>
       <x:c r="I6" s="15"/>
       <x:c r="J6" s="15"/>
       <x:c r="K6" s="15"/>
@@ -3985,49 +4243,95 @@
       <x:c r="N6" s="15"/>
       <x:c r="O6" s="15"/>
     </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="15"/>
-      <x:c r="B7" s="15"/>
-      <x:c r="C7" s="15"/>
-      <x:c r="D7" s="15"/>
-      <x:c r="E7" s="15"/>
-      <x:c r="F7" s="15"/>
-      <x:c r="G7" s="15"/>
-      <x:c r="H7" s="15"/>
-      <x:c r="I7" s="15"/>
-      <x:c r="J7" s="15"/>
-      <x:c r="K7" s="15"/>
-      <x:c r="L7" s="15"/>
-      <x:c r="M7" s="15"/>
-      <x:c r="N7" s="15"/>
-      <x:c r="O7" s="15"/>
-    </x:row>
-    <x:row r="8">
+    <x:row r="7" ht="34" customHeight="1">
+      <x:c r="A7" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B7" s="15" t="str">
+        <x:v>CSP</x:v>
+      </x:c>
+      <x:c r="C7" s="15" t="str">
+        <x:v>DEMO-CSP-03</x:v>
+      </x:c>
+      <x:c r="D7" s="15" t="str">
+        <x:v>Example Secure Assessment Portal</x:v>
+      </x:c>
+      <x:c r="E7" s="15" t="str">
+        <x:v>Fictional maximum-size example with five students and two supervisors.</x:v>
+      </x:c>
+      <x:c r="F7" s="15" t="str">
+        <x:v>CSP-DEMO</x:v>
+      </x:c>
+      <x:c r="G7" s="73" t="str">
+        <x:v>99000004</x:v>
+      </x:c>
+      <x:c r="H7" s="15" t="str">
+        <x:v>Example Student 04</x:v>
+      </x:c>
+      <x:c r="I7" s="15" t="str">
+        <x:v>DEMO-SUP-01</x:v>
+      </x:c>
+      <x:c r="J7" s="15" t="str">
+        <x:v>Example Supervisor Alpha</x:v>
+      </x:c>
+      <x:c r="K7" s="15" t="str">
+        <x:v>demo.faculty01@squ.edu.om;demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="L7" s="15" t="str">
+        <x:v>demo.faculty01@squ.edu.om;demo.faculty02@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="M7" s="15" t="str">
+        <x:v>demo.faculty02@squ.edu.om;demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="N7" s="15" t="str">
+        <x:v>demo.faculty01@squ.edu.om;demo.faculty02@squ.edu.om;demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="O7" s="15" t="str">
+        <x:v>demo.industry01@example.com;demo.industry02@example.com</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="15"/>
       <x:c r="B8" s="15"/>
-      <x:c r="C8" s="15"/>
+      <x:c r="C8" s="15" t="str">
+        <x:v>DEMO-CSP-03</x:v>
+      </x:c>
       <x:c r="D8" s="15"/>
       <x:c r="E8" s="15"/>
       <x:c r="F8" s="15"/>
-      <x:c r="G8" s="15"/>
-      <x:c r="H8" s="15"/>
-      <x:c r="I8" s="15"/>
-      <x:c r="J8" s="15"/>
+      <x:c r="G8" s="73" t="str">
+        <x:v>99000005</x:v>
+      </x:c>
+      <x:c r="H8" s="15" t="str">
+        <x:v>Example Student 05</x:v>
+      </x:c>
+      <x:c r="I8" s="15" t="str">
+        <x:v>DEMO-SUP-02</x:v>
+      </x:c>
+      <x:c r="J8" s="15" t="str">
+        <x:v>Example Supervisor Beta</x:v>
+      </x:c>
       <x:c r="K8" s="15"/>
       <x:c r="L8" s="15"/>
       <x:c r="M8" s="15"/>
       <x:c r="N8" s="15"/>
       <x:c r="O8" s="15"/>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="15"/>
       <x:c r="B9" s="15"/>
-      <x:c r="C9" s="15"/>
+      <x:c r="C9" s="15" t="str">
+        <x:v>DEMO-CSP-03</x:v>
+      </x:c>
       <x:c r="D9" s="15"/>
       <x:c r="E9" s="15"/>
       <x:c r="F9" s="15"/>
-      <x:c r="G9" s="15"/>
-      <x:c r="H9" s="15"/>
+      <x:c r="G9" s="73" t="str">
+        <x:v>99000006</x:v>
+      </x:c>
+      <x:c r="H9" s="15" t="str">
+        <x:v>Example Student 06</x:v>
+      </x:c>
       <x:c r="I9" s="15"/>
       <x:c r="J9" s="15"/>
       <x:c r="K9" s="15"/>
@@ -4036,15 +4340,21 @@
       <x:c r="N9" s="15"/>
       <x:c r="O9" s="15"/>
     </x:row>
-    <x:row r="10">
+    <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="15"/>
       <x:c r="B10" s="15"/>
-      <x:c r="C10" s="15"/>
+      <x:c r="C10" s="15" t="str">
+        <x:v>DEMO-CSP-03</x:v>
+      </x:c>
       <x:c r="D10" s="15"/>
       <x:c r="E10" s="15"/>
       <x:c r="F10" s="15"/>
-      <x:c r="G10" s="15"/>
-      <x:c r="H10" s="15"/>
+      <x:c r="G10" s="73" t="str">
+        <x:v>99000007</x:v>
+      </x:c>
+      <x:c r="H10" s="15" t="str">
+        <x:v>Example Student 07</x:v>
+      </x:c>
       <x:c r="I10" s="15"/>
       <x:c r="J10" s="15"/>
       <x:c r="K10" s="15"/>
@@ -4053,15 +4363,21 @@
       <x:c r="N10" s="15"/>
       <x:c r="O10" s="15"/>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="15"/>
       <x:c r="B11" s="15"/>
-      <x:c r="C11" s="15"/>
+      <x:c r="C11" s="15" t="str">
+        <x:v>DEMO-CSP-03</x:v>
+      </x:c>
       <x:c r="D11" s="15"/>
       <x:c r="E11" s="15"/>
       <x:c r="F11" s="15"/>
-      <x:c r="G11" s="15"/>
-      <x:c r="H11" s="15"/>
+      <x:c r="G11" s="73" t="str">
+        <x:v>99000008</x:v>
+      </x:c>
+      <x:c r="H11" s="15" t="str">
+        <x:v>Example Student 08</x:v>
+      </x:c>
       <x:c r="I11" s="15"/>
       <x:c r="J11" s="15"/>
       <x:c r="K11" s="15"/>
@@ -4070,32 +4386,68 @@
       <x:c r="N11" s="15"/>
       <x:c r="O11" s="15"/>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="15"/>
-      <x:c r="B12" s="15"/>
-      <x:c r="C12" s="15"/>
-      <x:c r="D12" s="15"/>
-      <x:c r="E12" s="15"/>
-      <x:c r="F12" s="15"/>
-      <x:c r="G12" s="15"/>
-      <x:c r="H12" s="15"/>
-      <x:c r="I12" s="15"/>
-      <x:c r="J12" s="15"/>
-      <x:c r="K12" s="15"/>
-      <x:c r="L12" s="15"/>
-      <x:c r="M12" s="15"/>
-      <x:c r="N12" s="15"/>
-      <x:c r="O12" s="15"/>
-    </x:row>
-    <x:row r="13">
+    <x:row r="12" ht="34" customHeight="1">
+      <x:c r="A12" s="15" t="str">
+        <x:v>2027</x:v>
+      </x:c>
+      <x:c r="B12" s="15" t="str">
+        <x:v>PSE</x:v>
+      </x:c>
+      <x:c r="C12" s="15" t="str">
+        <x:v>DEMO-PSE-04</x:v>
+      </x:c>
+      <x:c r="D12" s="15" t="str">
+        <x:v>Example Renewable Energy Project</x:v>
+      </x:c>
+      <x:c r="E12" s="15" t="str">
+        <x:v>Fictional example demonstrating two students, one supervisor, and a second industry guest.</x:v>
+      </x:c>
+      <x:c r="F12" s="15" t="str">
+        <x:v>PSE-DEMO</x:v>
+      </x:c>
+      <x:c r="G12" s="73" t="str">
+        <x:v>99000009</x:v>
+      </x:c>
+      <x:c r="H12" s="15" t="str">
+        <x:v>Example Student 09</x:v>
+      </x:c>
+      <x:c r="I12" s="15" t="str">
+        <x:v>DEMO-SUP-04</x:v>
+      </x:c>
+      <x:c r="J12" s="15" t="str">
+        <x:v>Example Supervisor Delta</x:v>
+      </x:c>
+      <x:c r="K12" s="15" t="str">
+        <x:v>demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="L12" s="15" t="str">
+        <x:v>demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="M12" s="15" t="str">
+        <x:v>demo.faculty01@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="N12" s="15" t="str">
+        <x:v>demo.faculty01@squ.edu.om;demo.faculty03@squ.edu.om</x:v>
+      </x:c>
+      <x:c r="O12" s="15" t="str">
+        <x:v>demo.industry02@example.com</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="34" customHeight="1">
       <x:c r="A13" s="15"/>
       <x:c r="B13" s="15"/>
-      <x:c r="C13" s="15"/>
+      <x:c r="C13" s="15" t="str">
+        <x:v>DEMO-PSE-04</x:v>
+      </x:c>
       <x:c r="D13" s="15"/>
       <x:c r="E13" s="15"/>
       <x:c r="F13" s="15"/>
-      <x:c r="G13" s="15"/>
-      <x:c r="H13" s="15"/>
+      <x:c r="G13" s="73" t="str">
+        <x:v>99000010</x:v>
+      </x:c>
+      <x:c r="H13" s="15" t="str">
+        <x:v>Example Student 10</x:v>
+      </x:c>
       <x:c r="I13" s="15"/>
       <x:c r="J13" s="15"/>
       <x:c r="K13" s="15"/>
@@ -4111,7 +4463,7 @@
       <x:c r="D14" s="15"/>
       <x:c r="E14" s="15"/>
       <x:c r="F14" s="15"/>
-      <x:c r="G14" s="15"/>
+      <x:c r="G14" s="73"/>
       <x:c r="H14" s="15"/>
       <x:c r="I14" s="15"/>
       <x:c r="J14" s="15"/>
@@ -4128,7 +4480,7 @@
       <x:c r="D15" s="15"/>
       <x:c r="E15" s="15"/>
       <x:c r="F15" s="15"/>
-      <x:c r="G15" s="15"/>
+      <x:c r="G15" s="73"/>
       <x:c r="H15" s="15"/>
       <x:c r="I15" s="15"/>
       <x:c r="J15" s="15"/>
@@ -4145,7 +4497,7 @@
       <x:c r="D16" s="15"/>
       <x:c r="E16" s="15"/>
       <x:c r="F16" s="15"/>
-      <x:c r="G16" s="15"/>
+      <x:c r="G16" s="73"/>
       <x:c r="H16" s="15"/>
       <x:c r="I16" s="15"/>
       <x:c r="J16" s="15"/>
@@ -4162,7 +4514,7 @@
       <x:c r="D17" s="15"/>
       <x:c r="E17" s="15"/>
       <x:c r="F17" s="15"/>
-      <x:c r="G17" s="15"/>
+      <x:c r="G17" s="73"/>
       <x:c r="H17" s="15"/>
       <x:c r="I17" s="15"/>
       <x:c r="J17" s="15"/>
@@ -4179,7 +4531,7 @@
       <x:c r="D18" s="15"/>
       <x:c r="E18" s="15"/>
       <x:c r="F18" s="15"/>
-      <x:c r="G18" s="15"/>
+      <x:c r="G18" s="73"/>
       <x:c r="H18" s="15"/>
       <x:c r="I18" s="15"/>
       <x:c r="J18" s="15"/>
@@ -4196,7 +4548,7 @@
       <x:c r="D19" s="15"/>
       <x:c r="E19" s="15"/>
       <x:c r="F19" s="15"/>
-      <x:c r="G19" s="15"/>
+      <x:c r="G19" s="73"/>
       <x:c r="H19" s="15"/>
       <x:c r="I19" s="15"/>
       <x:c r="J19" s="15"/>
@@ -4213,7 +4565,7 @@
       <x:c r="D20" s="15"/>
       <x:c r="E20" s="15"/>
       <x:c r="F20" s="15"/>
-      <x:c r="G20" s="15"/>
+      <x:c r="G20" s="73"/>
       <x:c r="H20" s="15"/>
       <x:c r="I20" s="15"/>
       <x:c r="J20" s="15"/>
@@ -4230,7 +4582,7 @@
       <x:c r="D21" s="15"/>
       <x:c r="E21" s="15"/>
       <x:c r="F21" s="15"/>
-      <x:c r="G21" s="15"/>
+      <x:c r="G21" s="73"/>
       <x:c r="H21" s="15"/>
       <x:c r="I21" s="15"/>
       <x:c r="J21" s="15"/>
@@ -4247,7 +4599,7 @@
       <x:c r="D22" s="15"/>
       <x:c r="E22" s="15"/>
       <x:c r="F22" s="15"/>
-      <x:c r="G22" s="15"/>
+      <x:c r="G22" s="73"/>
       <x:c r="H22" s="15"/>
       <x:c r="I22" s="15"/>
       <x:c r="J22" s="15"/>
@@ -4264,7 +4616,7 @@
       <x:c r="D23" s="15"/>
       <x:c r="E23" s="15"/>
       <x:c r="F23" s="15"/>
-      <x:c r="G23" s="15"/>
+      <x:c r="G23" s="73"/>
       <x:c r="H23" s="15"/>
       <x:c r="I23" s="15"/>
       <x:c r="J23" s="15"/>
@@ -4281,7 +4633,7 @@
       <x:c r="D24" s="15"/>
       <x:c r="E24" s="15"/>
       <x:c r="F24" s="15"/>
-      <x:c r="G24" s="15"/>
+      <x:c r="G24" s="73"/>
       <x:c r="H24" s="15"/>
       <x:c r="I24" s="15"/>
       <x:c r="J24" s="15"/>
@@ -4298,7 +4650,7 @@
       <x:c r="D25" s="15"/>
       <x:c r="E25" s="15"/>
       <x:c r="F25" s="15"/>
-      <x:c r="G25" s="15"/>
+      <x:c r="G25" s="73"/>
       <x:c r="H25" s="15"/>
       <x:c r="I25" s="15"/>
       <x:c r="J25" s="15"/>
@@ -4315,7 +4667,7 @@
       <x:c r="D26" s="15"/>
       <x:c r="E26" s="15"/>
       <x:c r="F26" s="15"/>
-      <x:c r="G26" s="15"/>
+      <x:c r="G26" s="73"/>
       <x:c r="H26" s="15"/>
       <x:c r="I26" s="15"/>
       <x:c r="J26" s="15"/>
@@ -4332,7 +4684,7 @@
       <x:c r="D27" s="15"/>
       <x:c r="E27" s="15"/>
       <x:c r="F27" s="15"/>
-      <x:c r="G27" s="15"/>
+      <x:c r="G27" s="73"/>
       <x:c r="H27" s="15"/>
       <x:c r="I27" s="15"/>
       <x:c r="J27" s="15"/>
@@ -4349,7 +4701,7 @@
       <x:c r="D28" s="15"/>
       <x:c r="E28" s="15"/>
       <x:c r="F28" s="15"/>
-      <x:c r="G28" s="15"/>
+      <x:c r="G28" s="73"/>
       <x:c r="H28" s="15"/>
       <x:c r="I28" s="15"/>
       <x:c r="J28" s="15"/>
@@ -4366,7 +4718,7 @@
       <x:c r="D29" s="15"/>
       <x:c r="E29" s="15"/>
       <x:c r="F29" s="15"/>
-      <x:c r="G29" s="15"/>
+      <x:c r="G29" s="73"/>
       <x:c r="H29" s="15"/>
       <x:c r="I29" s="15"/>
       <x:c r="J29" s="15"/>
@@ -4383,7 +4735,7 @@
       <x:c r="D30" s="15"/>
       <x:c r="E30" s="15"/>
       <x:c r="F30" s="15"/>
-      <x:c r="G30" s="15"/>
+      <x:c r="G30" s="73"/>
       <x:c r="H30" s="15"/>
       <x:c r="I30" s="15"/>
       <x:c r="J30" s="15"/>
@@ -4400,7 +4752,7 @@
       <x:c r="D31" s="15"/>
       <x:c r="E31" s="15"/>
       <x:c r="F31" s="15"/>
-      <x:c r="G31" s="15"/>
+      <x:c r="G31" s="73"/>
       <x:c r="H31" s="15"/>
       <x:c r="I31" s="15"/>
       <x:c r="J31" s="15"/>
@@ -4417,7 +4769,7 @@
       <x:c r="D32" s="15"/>
       <x:c r="E32" s="15"/>
       <x:c r="F32" s="15"/>
-      <x:c r="G32" s="15"/>
+      <x:c r="G32" s="73"/>
       <x:c r="H32" s="15"/>
       <x:c r="I32" s="15"/>
       <x:c r="J32" s="15"/>
@@ -4434,7 +4786,7 @@
       <x:c r="D33" s="15"/>
       <x:c r="E33" s="15"/>
       <x:c r="F33" s="15"/>
-      <x:c r="G33" s="15"/>
+      <x:c r="G33" s="73"/>
       <x:c r="H33" s="15"/>
       <x:c r="I33" s="15"/>
       <x:c r="J33" s="15"/>
@@ -4451,7 +4803,7 @@
       <x:c r="D34" s="15"/>
       <x:c r="E34" s="15"/>
       <x:c r="F34" s="15"/>
-      <x:c r="G34" s="15"/>
+      <x:c r="G34" s="73"/>
       <x:c r="H34" s="15"/>
       <x:c r="I34" s="15"/>
       <x:c r="J34" s="15"/>
@@ -4468,7 +4820,7 @@
       <x:c r="D35" s="15"/>
       <x:c r="E35" s="15"/>
       <x:c r="F35" s="15"/>
-      <x:c r="G35" s="15"/>
+      <x:c r="G35" s="73"/>
       <x:c r="H35" s="15"/>
       <x:c r="I35" s="15"/>
       <x:c r="J35" s="15"/>
@@ -4485,7 +4837,7 @@
       <x:c r="D36" s="15"/>
       <x:c r="E36" s="15"/>
       <x:c r="F36" s="15"/>
-      <x:c r="G36" s="15"/>
+      <x:c r="G36" s="73"/>
       <x:c r="H36" s="15"/>
       <x:c r="I36" s="15"/>
       <x:c r="J36" s="15"/>
@@ -4502,7 +4854,7 @@
       <x:c r="D37" s="15"/>
       <x:c r="E37" s="15"/>
       <x:c r="F37" s="15"/>
-      <x:c r="G37" s="15"/>
+      <x:c r="G37" s="73"/>
       <x:c r="H37" s="15"/>
       <x:c r="I37" s="15"/>
       <x:c r="J37" s="15"/>
@@ -4519,7 +4871,7 @@
       <x:c r="D38" s="15"/>
       <x:c r="E38" s="15"/>
       <x:c r="F38" s="15"/>
-      <x:c r="G38" s="15"/>
+      <x:c r="G38" s="73"/>
       <x:c r="H38" s="15"/>
       <x:c r="I38" s="15"/>
       <x:c r="J38" s="15"/>
@@ -4536,7 +4888,7 @@
       <x:c r="D39" s="15"/>
       <x:c r="E39" s="15"/>
       <x:c r="F39" s="15"/>
-      <x:c r="G39" s="15"/>
+      <x:c r="G39" s="73"/>
       <x:c r="H39" s="15"/>
       <x:c r="I39" s="15"/>
       <x:c r="J39" s="15"/>
@@ -4553,7 +4905,7 @@
       <x:c r="D40" s="15"/>
       <x:c r="E40" s="15"/>
       <x:c r="F40" s="15"/>
-      <x:c r="G40" s="15"/>
+      <x:c r="G40" s="73"/>
       <x:c r="H40" s="15"/>
       <x:c r="I40" s="15"/>
       <x:c r="J40" s="15"/>
@@ -4570,7 +4922,7 @@
       <x:c r="D41" s="15"/>
       <x:c r="E41" s="15"/>
       <x:c r="F41" s="15"/>
-      <x:c r="G41" s="15"/>
+      <x:c r="G41" s="73"/>
       <x:c r="H41" s="15"/>
       <x:c r="I41" s="15"/>
       <x:c r="J41" s="15"/>
@@ -4587,7 +4939,7 @@
       <x:c r="D42" s="15"/>
       <x:c r="E42" s="15"/>
       <x:c r="F42" s="15"/>
-      <x:c r="G42" s="15"/>
+      <x:c r="G42" s="73"/>
       <x:c r="H42" s="15"/>
       <x:c r="I42" s="15"/>
       <x:c r="J42" s="15"/>
@@ -4604,7 +4956,7 @@
       <x:c r="D43" s="15"/>
       <x:c r="E43" s="15"/>
       <x:c r="F43" s="15"/>
-      <x:c r="G43" s="15"/>
+      <x:c r="G43" s="73"/>
       <x:c r="H43" s="15"/>
       <x:c r="I43" s="15"/>
       <x:c r="J43" s="15"/>
@@ -4621,7 +4973,7 @@
       <x:c r="D44" s="15"/>
       <x:c r="E44" s="15"/>
       <x:c r="F44" s="15"/>
-      <x:c r="G44" s="15"/>
+      <x:c r="G44" s="73"/>
       <x:c r="H44" s="15"/>
       <x:c r="I44" s="15"/>
       <x:c r="J44" s="15"/>
@@ -4638,7 +4990,7 @@
       <x:c r="D45" s="15"/>
       <x:c r="E45" s="15"/>
       <x:c r="F45" s="15"/>
-      <x:c r="G45" s="15"/>
+      <x:c r="G45" s="73"/>
       <x:c r="H45" s="15"/>
       <x:c r="I45" s="15"/>
       <x:c r="J45" s="15"/>
@@ -4655,7 +5007,7 @@
       <x:c r="D46" s="15"/>
       <x:c r="E46" s="15"/>
       <x:c r="F46" s="15"/>
-      <x:c r="G46" s="15"/>
+      <x:c r="G46" s="73"/>
       <x:c r="H46" s="15"/>
       <x:c r="I46" s="15"/>
       <x:c r="J46" s="15"/>
@@ -4672,7 +5024,7 @@
       <x:c r="D47" s="15"/>
       <x:c r="E47" s="15"/>
       <x:c r="F47" s="15"/>
-      <x:c r="G47" s="15"/>
+      <x:c r="G47" s="73"/>
       <x:c r="H47" s="15"/>
       <x:c r="I47" s="15"/>
       <x:c r="J47" s="15"/>
@@ -4689,7 +5041,7 @@
       <x:c r="D48" s="15"/>
       <x:c r="E48" s="15"/>
       <x:c r="F48" s="15"/>
-      <x:c r="G48" s="15"/>
+      <x:c r="G48" s="73"/>
       <x:c r="H48" s="15"/>
       <x:c r="I48" s="15"/>
       <x:c r="J48" s="15"/>
@@ -4706,7 +5058,7 @@
       <x:c r="D49" s="15"/>
       <x:c r="E49" s="15"/>
       <x:c r="F49" s="15"/>
-      <x:c r="G49" s="15"/>
+      <x:c r="G49" s="73"/>
       <x:c r="H49" s="15"/>
       <x:c r="I49" s="15"/>
       <x:c r="J49" s="15"/>
@@ -4723,7 +5075,7 @@
       <x:c r="D50" s="15"/>
       <x:c r="E50" s="15"/>
       <x:c r="F50" s="15"/>
-      <x:c r="G50" s="15"/>
+      <x:c r="G50" s="73"/>
       <x:c r="H50" s="15"/>
       <x:c r="I50" s="15"/>
       <x:c r="J50" s="15"/>
@@ -4740,7 +5092,7 @@
       <x:c r="D51" s="15"/>
       <x:c r="E51" s="15"/>
       <x:c r="F51" s="15"/>
-      <x:c r="G51" s="15"/>
+      <x:c r="G51" s="73"/>
       <x:c r="H51" s="15"/>
       <x:c r="I51" s="15"/>
       <x:c r="J51" s="15"/>
@@ -4757,7 +5109,7 @@
       <x:c r="D52" s="15"/>
       <x:c r="E52" s="15"/>
       <x:c r="F52" s="15"/>
-      <x:c r="G52" s="15"/>
+      <x:c r="G52" s="73"/>
       <x:c r="H52" s="15"/>
       <x:c r="I52" s="15"/>
       <x:c r="J52" s="15"/>
@@ -4774,7 +5126,7 @@
       <x:c r="D53" s="15"/>
       <x:c r="E53" s="15"/>
       <x:c r="F53" s="15"/>
-      <x:c r="G53" s="15"/>
+      <x:c r="G53" s="73"/>
       <x:c r="H53" s="15"/>
       <x:c r="I53" s="15"/>
       <x:c r="J53" s="15"/>
@@ -4791,7 +5143,7 @@
       <x:c r="D54" s="15"/>
       <x:c r="E54" s="15"/>
       <x:c r="F54" s="15"/>
-      <x:c r="G54" s="15"/>
+      <x:c r="G54" s="73"/>
       <x:c r="H54" s="15"/>
       <x:c r="I54" s="15"/>
       <x:c r="J54" s="15"/>
@@ -4808,7 +5160,7 @@
       <x:c r="D55" s="15"/>
       <x:c r="E55" s="15"/>
       <x:c r="F55" s="15"/>
-      <x:c r="G55" s="15"/>
+      <x:c r="G55" s="73"/>
       <x:c r="H55" s="15"/>
       <x:c r="I55" s="15"/>
       <x:c r="J55" s="15"/>
@@ -4825,7 +5177,7 @@
       <x:c r="D56" s="15"/>
       <x:c r="E56" s="15"/>
       <x:c r="F56" s="15"/>
-      <x:c r="G56" s="15"/>
+      <x:c r="G56" s="73"/>
       <x:c r="H56" s="15"/>
       <x:c r="I56" s="15"/>
       <x:c r="J56" s="15"/>
@@ -4842,7 +5194,7 @@
       <x:c r="D57" s="15"/>
       <x:c r="E57" s="15"/>
       <x:c r="F57" s="15"/>
-      <x:c r="G57" s="15"/>
+      <x:c r="G57" s="73"/>
       <x:c r="H57" s="15"/>
       <x:c r="I57" s="15"/>
       <x:c r="J57" s="15"/>
@@ -4859,7 +5211,7 @@
       <x:c r="D58" s="15"/>
       <x:c r="E58" s="15"/>
       <x:c r="F58" s="15"/>
-      <x:c r="G58" s="15"/>
+      <x:c r="G58" s="73"/>
       <x:c r="H58" s="15"/>
       <x:c r="I58" s="15"/>
       <x:c r="J58" s="15"/>
@@ -4876,7 +5228,7 @@
       <x:c r="D59" s="15"/>
       <x:c r="E59" s="15"/>
       <x:c r="F59" s="15"/>
-      <x:c r="G59" s="15"/>
+      <x:c r="G59" s="73"/>
       <x:c r="H59" s="15"/>
       <x:c r="I59" s="15"/>
       <x:c r="J59" s="15"/>
@@ -4893,7 +5245,7 @@
       <x:c r="D60" s="15"/>
       <x:c r="E60" s="15"/>
       <x:c r="F60" s="15"/>
-      <x:c r="G60" s="15"/>
+      <x:c r="G60" s="73"/>
       <x:c r="H60" s="15"/>
       <x:c r="I60" s="15"/>
       <x:c r="J60" s="15"/>
@@ -4910,7 +5262,7 @@
       <x:c r="D61" s="15"/>
       <x:c r="E61" s="15"/>
       <x:c r="F61" s="15"/>
-      <x:c r="G61" s="15"/>
+      <x:c r="G61" s="73"/>
       <x:c r="H61" s="15"/>
       <x:c r="I61" s="15"/>
       <x:c r="J61" s="15"/>
@@ -4927,7 +5279,7 @@
       <x:c r="D62" s="15"/>
       <x:c r="E62" s="15"/>
       <x:c r="F62" s="15"/>
-      <x:c r="G62" s="15"/>
+      <x:c r="G62" s="73"/>
       <x:c r="H62" s="15"/>
       <x:c r="I62" s="15"/>
       <x:c r="J62" s="15"/>
@@ -4944,7 +5296,7 @@
       <x:c r="D63" s="15"/>
       <x:c r="E63" s="15"/>
       <x:c r="F63" s="15"/>
-      <x:c r="G63" s="15"/>
+      <x:c r="G63" s="73"/>
       <x:c r="H63" s="15"/>
       <x:c r="I63" s="15"/>
       <x:c r="J63" s="15"/>
@@ -4961,7 +5313,7 @@
       <x:c r="D64" s="15"/>
       <x:c r="E64" s="15"/>
       <x:c r="F64" s="15"/>
-      <x:c r="G64" s="15"/>
+      <x:c r="G64" s="73"/>
       <x:c r="H64" s="15"/>
       <x:c r="I64" s="15"/>
       <x:c r="J64" s="15"/>
@@ -4978,7 +5330,7 @@
       <x:c r="D65" s="15"/>
       <x:c r="E65" s="15"/>
       <x:c r="F65" s="15"/>
-      <x:c r="G65" s="15"/>
+      <x:c r="G65" s="73"/>
       <x:c r="H65" s="15"/>
       <x:c r="I65" s="15"/>
       <x:c r="J65" s="15"/>
@@ -4995,7 +5347,7 @@
       <x:c r="D66" s="15"/>
       <x:c r="E66" s="15"/>
       <x:c r="F66" s="15"/>
-      <x:c r="G66" s="15"/>
+      <x:c r="G66" s="73"/>
       <x:c r="H66" s="15"/>
       <x:c r="I66" s="15"/>
       <x:c r="J66" s="15"/>
@@ -5012,7 +5364,7 @@
       <x:c r="D67" s="15"/>
       <x:c r="E67" s="15"/>
       <x:c r="F67" s="15"/>
-      <x:c r="G67" s="15"/>
+      <x:c r="G67" s="73"/>
       <x:c r="H67" s="15"/>
       <x:c r="I67" s="15"/>
       <x:c r="J67" s="15"/>
@@ -5029,7 +5381,7 @@
       <x:c r="D68" s="15"/>
       <x:c r="E68" s="15"/>
       <x:c r="F68" s="15"/>
-      <x:c r="G68" s="15"/>
+      <x:c r="G68" s="73"/>
       <x:c r="H68" s="15"/>
       <x:c r="I68" s="15"/>
       <x:c r="J68" s="15"/>
@@ -5046,7 +5398,7 @@
       <x:c r="D69" s="15"/>
       <x:c r="E69" s="15"/>
       <x:c r="F69" s="15"/>
-      <x:c r="G69" s="15"/>
+      <x:c r="G69" s="73"/>
       <x:c r="H69" s="15"/>
       <x:c r="I69" s="15"/>
       <x:c r="J69" s="15"/>
@@ -5063,7 +5415,7 @@
       <x:c r="D70" s="15"/>
       <x:c r="E70" s="15"/>
       <x:c r="F70" s="15"/>
-      <x:c r="G70" s="15"/>
+      <x:c r="G70" s="73"/>
       <x:c r="H70" s="15"/>
       <x:c r="I70" s="15"/>
       <x:c r="J70" s="15"/>
@@ -5080,7 +5432,7 @@
       <x:c r="D71" s="15"/>
       <x:c r="E71" s="15"/>
       <x:c r="F71" s="15"/>
-      <x:c r="G71" s="15"/>
+      <x:c r="G71" s="73"/>
       <x:c r="H71" s="15"/>
       <x:c r="I71" s="15"/>
       <x:c r="J71" s="15"/>
@@ -5097,7 +5449,7 @@
       <x:c r="D72" s="15"/>
       <x:c r="E72" s="15"/>
       <x:c r="F72" s="15"/>
-      <x:c r="G72" s="15"/>
+      <x:c r="G72" s="73"/>
       <x:c r="H72" s="15"/>
       <x:c r="I72" s="15"/>
       <x:c r="J72" s="15"/>
@@ -5114,7 +5466,7 @@
       <x:c r="D73" s="15"/>
       <x:c r="E73" s="15"/>
       <x:c r="F73" s="15"/>
-      <x:c r="G73" s="15"/>
+      <x:c r="G73" s="73"/>
       <x:c r="H73" s="15"/>
       <x:c r="I73" s="15"/>
       <x:c r="J73" s="15"/>
@@ -5131,7 +5483,7 @@
       <x:c r="D74" s="15"/>
       <x:c r="E74" s="15"/>
       <x:c r="F74" s="15"/>
-      <x:c r="G74" s="15"/>
+      <x:c r="G74" s="73"/>
       <x:c r="H74" s="15"/>
       <x:c r="I74" s="15"/>
       <x:c r="J74" s="15"/>
@@ -5148,7 +5500,7 @@
       <x:c r="D75" s="15"/>
       <x:c r="E75" s="15"/>
       <x:c r="F75" s="15"/>
-      <x:c r="G75" s="15"/>
+      <x:c r="G75" s="73"/>
       <x:c r="H75" s="15"/>
       <x:c r="I75" s="15"/>
       <x:c r="J75" s="15"/>
@@ -5165,7 +5517,7 @@
       <x:c r="D76" s="15"/>
       <x:c r="E76" s="15"/>
       <x:c r="F76" s="15"/>
-      <x:c r="G76" s="15"/>
+      <x:c r="G76" s="73"/>
       <x:c r="H76" s="15"/>
       <x:c r="I76" s="15"/>
       <x:c r="J76" s="15"/>
@@ -5182,7 +5534,7 @@
       <x:c r="D77" s="15"/>
       <x:c r="E77" s="15"/>
       <x:c r="F77" s="15"/>
-      <x:c r="G77" s="15"/>
+      <x:c r="G77" s="73"/>
       <x:c r="H77" s="15"/>
       <x:c r="I77" s="15"/>
       <x:c r="J77" s="15"/>
@@ -5199,7 +5551,7 @@
       <x:c r="D78" s="15"/>
       <x:c r="E78" s="15"/>
       <x:c r="F78" s="15"/>
-      <x:c r="G78" s="15"/>
+      <x:c r="G78" s="73"/>
       <x:c r="H78" s="15"/>
       <x:c r="I78" s="15"/>
       <x:c r="J78" s="15"/>
@@ -5216,7 +5568,7 @@
       <x:c r="D79" s="15"/>
       <x:c r="E79" s="15"/>
       <x:c r="F79" s="15"/>
-      <x:c r="G79" s="15"/>
+      <x:c r="G79" s="73"/>
       <x:c r="H79" s="15"/>
       <x:c r="I79" s="15"/>
       <x:c r="J79" s="15"/>
@@ -5233,7 +5585,7 @@
       <x:c r="D80" s="15"/>
       <x:c r="E80" s="15"/>
       <x:c r="F80" s="15"/>
-      <x:c r="G80" s="15"/>
+      <x:c r="G80" s="73"/>
       <x:c r="H80" s="15"/>
       <x:c r="I80" s="15"/>
       <x:c r="J80" s="15"/>
@@ -5250,7 +5602,7 @@
       <x:c r="D81" s="15"/>
       <x:c r="E81" s="15"/>
       <x:c r="F81" s="15"/>
-      <x:c r="G81" s="15"/>
+      <x:c r="G81" s="73"/>
       <x:c r="H81" s="15"/>
       <x:c r="I81" s="15"/>
       <x:c r="J81" s="15"/>
@@ -5267,7 +5619,7 @@
       <x:c r="D82" s="15"/>
       <x:c r="E82" s="15"/>
       <x:c r="F82" s="15"/>
-      <x:c r="G82" s="15"/>
+      <x:c r="G82" s="73"/>
       <x:c r="H82" s="15"/>
       <x:c r="I82" s="15"/>
       <x:c r="J82" s="15"/>
@@ -5284,7 +5636,7 @@
       <x:c r="D83" s="15"/>
       <x:c r="E83" s="15"/>
       <x:c r="F83" s="15"/>
-      <x:c r="G83" s="15"/>
+      <x:c r="G83" s="73"/>
       <x:c r="H83" s="15"/>
       <x:c r="I83" s="15"/>
       <x:c r="J83" s="15"/>
@@ -5301,7 +5653,7 @@
       <x:c r="D84" s="15"/>
       <x:c r="E84" s="15"/>
       <x:c r="F84" s="15"/>
-      <x:c r="G84" s="15"/>
+      <x:c r="G84" s="73"/>
       <x:c r="H84" s="15"/>
       <x:c r="I84" s="15"/>
       <x:c r="J84" s="15"/>
@@ -5318,7 +5670,7 @@
       <x:c r="D85" s="15"/>
       <x:c r="E85" s="15"/>
       <x:c r="F85" s="15"/>
-      <x:c r="G85" s="15"/>
+      <x:c r="G85" s="73"/>
       <x:c r="H85" s="15"/>
       <x:c r="I85" s="15"/>
       <x:c r="J85" s="15"/>
@@ -5335,7 +5687,7 @@
       <x:c r="D86" s="15"/>
       <x:c r="E86" s="15"/>
       <x:c r="F86" s="15"/>
-      <x:c r="G86" s="15"/>
+      <x:c r="G86" s="73"/>
       <x:c r="H86" s="15"/>
       <x:c r="I86" s="15"/>
       <x:c r="J86" s="15"/>
@@ -5352,7 +5704,7 @@
       <x:c r="D87" s="15"/>
       <x:c r="E87" s="15"/>
       <x:c r="F87" s="15"/>
-      <x:c r="G87" s="15"/>
+      <x:c r="G87" s="73"/>
       <x:c r="H87" s="15"/>
       <x:c r="I87" s="15"/>
       <x:c r="J87" s="15"/>
@@ -5369,7 +5721,7 @@
       <x:c r="D88" s="15"/>
       <x:c r="E88" s="15"/>
       <x:c r="F88" s="15"/>
-      <x:c r="G88" s="15"/>
+      <x:c r="G88" s="73"/>
       <x:c r="H88" s="15"/>
       <x:c r="I88" s="15"/>
       <x:c r="J88" s="15"/>
@@ -5386,7 +5738,7 @@
       <x:c r="D89" s="15"/>
       <x:c r="E89" s="15"/>
       <x:c r="F89" s="15"/>
-      <x:c r="G89" s="15"/>
+      <x:c r="G89" s="73"/>
       <x:c r="H89" s="15"/>
       <x:c r="I89" s="15"/>
       <x:c r="J89" s="15"/>
@@ -5403,7 +5755,7 @@
       <x:c r="D90" s="15"/>
       <x:c r="E90" s="15"/>
       <x:c r="F90" s="15"/>
-      <x:c r="G90" s="15"/>
+      <x:c r="G90" s="73"/>
       <x:c r="H90" s="15"/>
       <x:c r="I90" s="15"/>
       <x:c r="J90" s="15"/>
@@ -5420,7 +5772,7 @@
       <x:c r="D91" s="15"/>
       <x:c r="E91" s="15"/>
       <x:c r="F91" s="15"/>
-      <x:c r="G91" s="15"/>
+      <x:c r="G91" s="73"/>
       <x:c r="H91" s="15"/>
       <x:c r="I91" s="15"/>
       <x:c r="J91" s="15"/>
@@ -5437,7 +5789,7 @@
       <x:c r="D92" s="15"/>
       <x:c r="E92" s="15"/>
       <x:c r="F92" s="15"/>
-      <x:c r="G92" s="15"/>
+      <x:c r="G92" s="73"/>
       <x:c r="H92" s="15"/>
       <x:c r="I92" s="15"/>
       <x:c r="J92" s="15"/>
@@ -5454,7 +5806,7 @@
       <x:c r="D93" s="15"/>
       <x:c r="E93" s="15"/>
       <x:c r="F93" s="15"/>
-      <x:c r="G93" s="15"/>
+      <x:c r="G93" s="73"/>
       <x:c r="H93" s="15"/>
       <x:c r="I93" s="15"/>
       <x:c r="J93" s="15"/>
@@ -5471,7 +5823,7 @@
       <x:c r="D94" s="15"/>
       <x:c r="E94" s="15"/>
       <x:c r="F94" s="15"/>
-      <x:c r="G94" s="15"/>
+      <x:c r="G94" s="73"/>
       <x:c r="H94" s="15"/>
       <x:c r="I94" s="15"/>
       <x:c r="J94" s="15"/>
@@ -5488,7 +5840,7 @@
       <x:c r="D95" s="15"/>
       <x:c r="E95" s="15"/>
       <x:c r="F95" s="15"/>
-      <x:c r="G95" s="15"/>
+      <x:c r="G95" s="73"/>
       <x:c r="H95" s="15"/>
       <x:c r="I95" s="15"/>
       <x:c r="J95" s="15"/>
@@ -5505,7 +5857,7 @@
       <x:c r="D96" s="15"/>
       <x:c r="E96" s="15"/>
       <x:c r="F96" s="15"/>
-      <x:c r="G96" s="15"/>
+      <x:c r="G96" s="73"/>
       <x:c r="H96" s="15"/>
       <x:c r="I96" s="15"/>
       <x:c r="J96" s="15"/>
@@ -5522,7 +5874,7 @@
       <x:c r="D97" s="15"/>
       <x:c r="E97" s="15"/>
       <x:c r="F97" s="15"/>
-      <x:c r="G97" s="15"/>
+      <x:c r="G97" s="73"/>
       <x:c r="H97" s="15"/>
       <x:c r="I97" s="15"/>
       <x:c r="J97" s="15"/>
@@ -5539,7 +5891,7 @@
       <x:c r="D98" s="15"/>
       <x:c r="E98" s="15"/>
       <x:c r="F98" s="15"/>
-      <x:c r="G98" s="15"/>
+      <x:c r="G98" s="73"/>
       <x:c r="H98" s="15"/>
       <x:c r="I98" s="15"/>
       <x:c r="J98" s="15"/>
@@ -5556,7 +5908,7 @@
       <x:c r="D99" s="15"/>
       <x:c r="E99" s="15"/>
       <x:c r="F99" s="15"/>
-      <x:c r="G99" s="15"/>
+      <x:c r="G99" s="73"/>
       <x:c r="H99" s="15"/>
       <x:c r="I99" s="15"/>
       <x:c r="J99" s="15"/>
@@ -5573,7 +5925,7 @@
       <x:c r="D100" s="15"/>
       <x:c r="E100" s="15"/>
       <x:c r="F100" s="15"/>
-      <x:c r="G100" s="15"/>
+      <x:c r="G100" s="73"/>
       <x:c r="H100" s="15"/>
       <x:c r="I100" s="15"/>
       <x:c r="J100" s="15"/>

--- a/docs/templates/modele_initialisation_plateforme_fyp.xlsx
+++ b/docs/templates/modele_initialisation_plateforme_fyp.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCTIONS" sheetId="1" r:id="R83a9c2582aa34355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" r:id="R75359ad1fa584cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADMINISTRATORS" sheetId="3" r:id="R74f2da951e3f496d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COORDINATORS" sheetId="4" r:id="Ra9227190c5b2435e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUPERVISORS" sheetId="5" r:id="R1a54a4880fbe4b29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REPORT_EVALUATORS" sheetId="6" r:id="Re7e4e1a5cf064f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACULTY_EVALUATORS" sheetId="7" r:id="Rc639571be0194914"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDUSTRY_GUESTS" sheetId="8" r:id="Rd49eea0892ce43eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASES" sheetId="9" r:id="R16ba620c1d74480a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJECT_ASSIGNMENTS" sheetId="10" r:id="R255e91e654ca4b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCTIONS" sheetId="1" r:id="R0b0c4e2efc454b0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" r:id="Ra4a796c7120b4c7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ADMINISTRATORS" sheetId="3" r:id="R275db08e1b334218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COORDINATORS" sheetId="4" r:id="Rc5f73a317a72449b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SUPERVISORS" sheetId="5" r:id="Re76bba599eca46ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REPORT_EVALUATORS" sheetId="6" r:id="R120d9029df574585"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FACULTY_EVALUATORS" sheetId="7" r:id="Ra019a9b5b06f4409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INDUSTRY_GUESTS" sheetId="8" r:id="R209cdcd4e2294b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PHASES" sheetId="9" r:id="Rcfa69ea128964a41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROJECT_ASSIGNMENTS" sheetId="10" r:id="R538eb04e74b741e3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -638,7 +638,7 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="15" t="str">
-        <x:v>Replace each internal actor example with the official SQU identity. Do not add passwords; internal users authenticate through SQU SSO.</x:v>
+        <x:v>Replace each actor example with the official identity. Do not add passwords. Each user completes Sign up with the pre-registered email and a verification code sent by email.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="32.25" customHeight="1">
@@ -646,7 +646,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="15" t="str">
-        <x:v>For an Industry Guest, provide a future Access Expires At value and keep status PENDING_INVITATION. The platform sends a one-time activation link.</x:v>
+        <x:v>For an Industry Guest, provide a future Access Expires At value and use PENDING_ACTIVATION. The guest completes the same secure Sign up process.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="32.25" customHeight="1">
@@ -686,7 +686,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="15" t="str">
-        <x:v>Upload the workbook in Excel Imports, run Preview, correct every error, then confirm the atomic import.</x:v>
+        <x:v>Upload the workbook in Excel Imports, run Preview, correct every error, then confirm the atomic import. To create an account active immediately, use Accounts and access after import.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -848,7 +848,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8b921f98c8a4baa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reb306fab5f414d57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -928,7 +928,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc48024530e94467e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4061c9e29a04093"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -999,13 +999,18 @@
       <x:c r="G2" s="13" t="str"/>
       <x:c r="H2" s="30" t="str"/>
       <x:c r="I2" s="30" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"PENDING_ACTIVATION,ACTIVE,INACTIVE,SUSPENDED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb14fe8764d14e2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865ff094ba264c06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1076,13 +1081,18 @@
       <x:c r="G2" s="13" t="str"/>
       <x:c r="H2" s="30" t="str"/>
       <x:c r="I2" s="30" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"PENDING_ACTIVATION,ACTIVE,INACTIVE,SUSPENDED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Radefc814626349db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R068925014cde4922"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1153,7 +1163,7 @@
       <x:c r="G2" s="31" t="str"/>
       <x:c r="H2" s="28" t="str"/>
       <x:c r="I2" s="28" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="23.25" customHeight="1">
@@ -1178,13 +1188,18 @@
       <x:c r="G3" s="32" t="str"/>
       <x:c r="H3" s="29" t="str"/>
       <x:c r="I3" s="29" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"PENDING_ACTIVATION,ACTIVE,INACTIVE,SUSPENDED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c6db553ecc94b8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdcd344a08eb44c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1255,13 +1270,18 @@
       <x:c r="G2" s="13" t="str"/>
       <x:c r="H2" s="30" t="str"/>
       <x:c r="I2" s="30" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"PENDING_ACTIVATION,ACTIVE,INACTIVE,SUSPENDED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc72c323aa50944d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ffa7597e31a4406"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1332,13 +1352,18 @@
       <x:c r="G2" s="13" t="str"/>
       <x:c r="H2" s="30" t="str"/>
       <x:c r="I2" s="30" t="str">
-        <x:v>ACTIVE</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"PENDING_ACTIVATION,ACTIVE,INACTIVE,SUSPENDED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1add5dd1ba7c41b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ef2ab0454bb4e7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1411,13 +1436,18 @@
         <x:v>2028-06-30T23:59</x:v>
       </x:c>
       <x:c r="I2" s="30" t="str">
-        <x:v>PENDING_INVITATION</x:v>
+        <x:v>PENDING_ACTIVATION</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I500">
+      <x:formula1>"PENDING_ACTIVATION,ACTIVE,INACTIVE,SUSPENDED"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R033841fe23524c3d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ad566af74f340cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1505,7 +1535,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R188f9b0532e94594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07aef37095ca4374"/>
   </x:tableParts>
 </x:worksheet>
 </file>